--- a/Models/КРС/results/КРС - Результаты прогнозов Prophet.xlsx
+++ b/Models/КРС/results/КРС - Результаты прогнозов Prophet.xlsx
@@ -478,31 +478,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>124.23</v>
+        <v>511.26</v>
       </c>
       <c r="E2" t="n">
-        <v>114.48</v>
+        <v>495.42</v>
       </c>
       <c r="F2" t="n">
-        <v>3.09</v>
+        <v>19.22</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[3902.77, 3284.17, 3730.77]</t>
+          <t>[1759.78, 2565.87, 2118.73]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[4035.37, 3446.55, 3779.21]</t>
+          <t>[2412.7, 2909.66, 2608.27]</t>
         </is>
       </c>
     </row>
@@ -514,31 +514,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>230.81</v>
+        <v>420.06</v>
       </c>
       <c r="E3" t="n">
-        <v>192.56</v>
+        <v>407.86</v>
       </c>
       <c r="F3" t="n">
-        <v>5.31</v>
+        <v>13.38</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[3279.52, 3728.15, 3331.45]</t>
+          <t>[2633.93, 2179.81, 3129.8]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[3446.55, 3779.21, 3691.05]</t>
+          <t>[2909.66, 2608.27, 3649.19]</t>
         </is>
       </c>
     </row>
@@ -550,31 +550,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>254</v>
+        <v>459.04</v>
       </c>
       <c r="E4" t="n">
-        <v>217.26</v>
+        <v>457.81</v>
       </c>
       <c r="F4" t="n">
-        <v>5.95</v>
+        <v>13.46</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[3739.88, 3337.62, 3315.85]</t>
+          <t>[2193.67, 3152.81, 3791.12]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[3779.21, 3691.05, 3574.86]</t>
+          <t>[2608.27, 3649.19, 4253.58]</t>
         </is>
       </c>
     </row>
@@ -586,31 +586,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>284.15</v>
+        <v>356.61</v>
       </c>
       <c r="E5" t="n">
-        <v>281.32</v>
+        <v>297.23</v>
       </c>
       <c r="F5" t="n">
-        <v>7.52</v>
+        <v>7.6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[3363.24, 3344.64, 3665.48]</t>
+          <t>[3188.29, 3842.87, 3968.08]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[3691.05, 3574.86, 3951.41]</t>
+          <t>[3649.19, 4253.58, 3947.99]</t>
         </is>
       </c>
     </row>
@@ -622,31 +622,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>261.23</v>
+        <v>226.8</v>
       </c>
       <c r="E6" t="n">
-        <v>259.8</v>
+        <v>195.88</v>
       </c>
       <c r="F6" t="n">
-        <v>9.050000000000001</v>
+        <v>4.87</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[3352.93, 3679.26, 1744.16]</t>
+          <t>[3899.86, 4034.64, 3441.66]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[3574.86, 3951.41, 2029.47]</t>
+          <t>[4253.58, 3947.99, 3588.93]</t>
         </is>
       </c>
     </row>
@@ -658,31 +658,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>455.43</v>
+        <v>238.97</v>
       </c>
       <c r="E7" t="n">
-        <v>408.58</v>
+        <v>200.28</v>
       </c>
       <c r="F7" t="n">
-        <v>16.28</v>
+        <v>4.85</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[3695.12, 1752.88, 1719.84]</t>
+          <t>[4139.45, 3543.7, 3951.37]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[3951.41, 2029.47, 2412.7]</t>
+          <t>[3947.99, 3588.93, 4315.53]</t>
         </is>
       </c>
     </row>
@@ -694,31 +694,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>479.98</v>
+        <v>302.73</v>
       </c>
       <c r="E8" t="n">
-        <v>447.18</v>
+        <v>269.9</v>
       </c>
       <c r="F8" t="n">
-        <v>18.31</v>
+        <v>6.62</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[1761.86, 1729.35, 2519.08]</t>
+          <t>[3505.92, 3907.37, 3615.59]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[2029.47, 2412.7, 2909.66]</t>
+          <t>[3588.93, 4315.53, 3934.11]</t>
         </is>
       </c>
     </row>
@@ -730,31 +730,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>511.26</v>
+        <v>248.65</v>
       </c>
       <c r="E9" t="n">
-        <v>495.42</v>
+        <v>226.65</v>
       </c>
       <c r="F9" t="n">
-        <v>19.22</v>
+        <v>5.54</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[1759.78, 2565.87, 2118.73]</t>
+          <t>[3977.18, 3683.77, 3675.71]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[2412.7, 2909.66, 2608.27]</t>
+          <t>[4315.53, 3934.11, 3766.97]</t>
         </is>
       </c>
     </row>
@@ -766,31 +766,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>420.06</v>
+        <v>163.38</v>
       </c>
       <c r="E10" t="n">
-        <v>407.86</v>
+        <v>132.89</v>
       </c>
       <c r="F10" t="n">
-        <v>13.38</v>
+        <v>3.19</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[2633.93, 2179.81, 3129.8]</t>
+          <t>[3777.19, 3773.31, 4111.13]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[2909.66, 2608.27, 3649.19]</t>
+          <t>[3934.11, 3766.97, 4346.53]</t>
         </is>
       </c>
     </row>
@@ -802,31 +802,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>459.04</v>
+        <v>257.28</v>
       </c>
       <c r="E11" t="n">
-        <v>457.81</v>
+        <v>213.84</v>
       </c>
       <c r="F11" t="n">
-        <v>13.46</v>
+        <v>7.46</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[2193.67, 3152.81, 3791.12]</t>
+          <t>[3843.77, 4193.09, 2035.35]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[2608.27, 3649.19, 4253.58]</t>
+          <t>[3766.97, 4346.53, 2446.61]</t>
         </is>
       </c>
     </row>
@@ -838,31 +838,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>589.85</v>
+        <v>699.61</v>
       </c>
       <c r="E12" t="n">
-        <v>470.3</v>
+        <v>640.36</v>
       </c>
       <c r="F12" t="n">
-        <v>8.1</v>
+        <v>15.14</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[4549.67, 4333.22, 5659.53]</t>
+          <t>[3867.73, 4840.33, 2869.91]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[4438.18, 4677.05, 6615.11]</t>
+          <t>[4406.21, 5198.02, 3894.84]</t>
         </is>
       </c>
     </row>
@@ -874,31 +874,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1006.47</v>
+        <v>621.08</v>
       </c>
       <c r="E13" t="n">
-        <v>908.48</v>
+        <v>520.71</v>
       </c>
       <c r="F13" t="n">
-        <v>15.35</v>
+        <v>12.46</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[4327.97, 5643.19, 4469.85]</t>
+          <t>[4884.82, 2896.73, 4138.92]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[4677.05, 6615.11, 5874.29]</t>
+          <t>[5198.02, 3894.84, 4389.74]</t>
         </is>
       </c>
     </row>
@@ -910,31 +910,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>984.65</v>
+        <v>611.97</v>
       </c>
       <c r="E14" t="n">
-        <v>941.0700000000001</v>
+        <v>506.58</v>
       </c>
       <c r="F14" t="n">
-        <v>15.72</v>
+        <v>11.22</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[5746.83, 4547.66, 4856.99]</t>
+          <t>[2903.45, 4148.73, 10316.63]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[6615.11, 5874.29, 5485.3]</t>
+          <t>[3894.84, 4389.74, 10603.99]</t>
         </is>
       </c>
     </row>
@@ -946,31 +946,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1040.47</v>
+        <v>170.49</v>
       </c>
       <c r="E15" t="n">
-        <v>996.09</v>
+        <v>157.3</v>
       </c>
       <c r="F15" t="n">
-        <v>15.98</v>
+        <v>3.23</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[4591.29, 4904.4, 6122.1]</t>
+          <t>[4223.45, 10531.31, 4233.3]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[5874.29, 5485.3, 7246.46]</t>
+          <t>[4389.74, 10603.99, 4466.24]</t>
         </is>
       </c>
     </row>
@@ -982,31 +982,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>719.8200000000001</v>
+        <v>128.81</v>
       </c>
       <c r="E16" t="n">
-        <v>682.15</v>
+        <v>127.68</v>
       </c>
       <c r="F16" t="n">
-        <v>12.4</v>
+        <v>2.27</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[4975.87, 6239.54, 3254.23]</t>
+          <t>[10735.97, 4320.23, 4443.18]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[5485.3, 7246.46, 3784.33]</t>
+          <t>[10603.99, 4466.24, 4548.23]</t>
         </is>
       </c>
     </row>
@@ -1018,31 +1018,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>714.33</v>
+        <v>531.14</v>
       </c>
       <c r="E17" t="n">
-        <v>688.0599999999999</v>
+        <v>361.24</v>
       </c>
       <c r="F17" t="n">
-        <v>13.41</v>
+        <v>5.9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[6296.95, 3290.23, 3785.65]</t>
+          <t>[4357.94, 4484.11, 5663.1]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[7246.46, 3784.33, 4406.21]</t>
+          <t>[4466.24, 4548.23, 6574.41]</t>
         </is>
       </c>
     </row>
@@ -1054,31 +1054,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>477.65</v>
+        <v>788.85</v>
       </c>
       <c r="E18" t="n">
-        <v>471.89</v>
+        <v>645.7</v>
       </c>
       <c r="F18" t="n">
-        <v>10.82</v>
+        <v>10.63</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[3334.02, 3834.88, 4804.0]</t>
+          <t>[4529.74, 5729.16, 4692.96]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[3784.33, 4406.21, 5198.02]</t>
+          <t>[4548.23, 6574.41, 5766.31]</t>
         </is>
       </c>
     </row>
@@ -1090,31 +1090,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>699.61</v>
+        <v>795.02</v>
       </c>
       <c r="E19" t="n">
-        <v>640.36</v>
+        <v>772.92</v>
       </c>
       <c r="F19" t="n">
-        <v>15.14</v>
+        <v>13.05</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[3867.73, 4840.33, 2869.91]</t>
+          <t>[5809.62, 4761.45, 4897.12]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[4406.21, 5198.02, 3894.84]</t>
+          <t>[6574.41, 5766.31, 5446.24]</t>
         </is>
       </c>
     </row>
@@ -1126,31 +1126,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>621.08</v>
+        <v>671.91</v>
       </c>
       <c r="E20" t="n">
-        <v>520.71</v>
+        <v>640.37</v>
       </c>
       <c r="F20" t="n">
-        <v>12.46</v>
+        <v>10.68</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[4884.82, 2896.73, 4138.92]</t>
+          <t>[4841.16, 4983.91, 6576.23]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[5198.02, 3894.84, 4389.74]</t>
+          <t>[5766.31, 5446.24, 7109.86]</t>
         </is>
       </c>
     </row>
@@ -1162,31 +1162,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>611.97</v>
+        <v>260.8</v>
       </c>
       <c r="E21" t="n">
-        <v>506.58</v>
+        <v>252.06</v>
       </c>
       <c r="F21" t="n">
-        <v>11.22</v>
+        <v>4.71</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[2903.45, 4148.73, 10316.63]</t>
+          <t>[5149.48, 6807.87, 3398.0]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[3894.84, 4389.74, 10603.99]</t>
+          <t>[5446.24, 7109.86, 3555.44]</t>
         </is>
       </c>
     </row>
@@ -1198,31 +1198,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1471.3</v>
+        <v>3495.09</v>
       </c>
       <c r="E22" t="n">
-        <v>1168.76</v>
+        <v>3300.31</v>
       </c>
       <c r="F22" t="n">
-        <v>22.07</v>
+        <v>38.28</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[2681.88, 1871.0, 6852.72]</t>
+          <t>[3090.99, 6784.76, 6262.16]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[2868.77, 2841.48, 9201.63]</t>
+          <t>[5453.39, 11705.42, 8880.02]</t>
         </is>
       </c>
     </row>
@@ -1234,31 +1234,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1551.06</v>
+        <v>2997.54</v>
       </c>
       <c r="E23" t="n">
-        <v>1411.66</v>
+        <v>2460.26</v>
       </c>
       <c r="F23" t="n">
-        <v>30.55</v>
+        <v>24.35</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[1872.83, 6881.22, 1978.93]</t>
+          <t>[7080.62, 6561.5, 6320.23]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[2841.48, 9201.63, 2924.85]</t>
+          <t>[11705.42, 8880.02, 5882.78]</t>
         </is>
       </c>
     </row>
@@ -1270,31 +1270,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1413.28</v>
+        <v>1376.09</v>
       </c>
       <c r="E24" t="n">
-        <v>1351.49</v>
+        <v>1355.94</v>
       </c>
       <c r="F24" t="n">
-        <v>25.75</v>
+        <v>16.15</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[7449.49, 2142.25, 3311.01]</t>
+          <t>[7196.13, 7030.97, 11164.63]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[9201.63, 2924.85, 4830.75]</t>
+          <t>[8880.02, 5882.78, 12400.36]</t>
         </is>
       </c>
     </row>
@@ -1306,31 +1306,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3002.96</v>
+        <v>924.21</v>
       </c>
       <c r="E25" t="n">
-        <v>2382.14</v>
+        <v>726.73</v>
       </c>
       <c r="F25" t="n">
-        <v>30.66</v>
+        <v>10.47</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[2173.2, 3371.45, 8750.67]</t>
+          <t>[7319.53, 11695.58, 3030.99]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[2924.85, 4830.75, 13686.13]</t>
+          <t>[5882.78, 12400.36, 2992.34]</t>
         </is>
       </c>
     </row>
@@ -1342,31 +1342,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2858.97</v>
+        <v>543.77</v>
       </c>
       <c r="E26" t="n">
-        <v>2283.98</v>
+        <v>461.28</v>
       </c>
       <c r="F26" t="n">
-        <v>32.48</v>
+        <v>10.89</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[3455.29, 8994.25, 1477.3]</t>
+          <t>[11807.43, 3054.08, 2095.53]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[4830.75, 13686.13, 2261.91]</t>
+          <t>[12400.36, 2992.34, 2824.69]</t>
         </is>
       </c>
     </row>
@@ -1378,31 +1378,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3012.05</v>
+        <v>384.39</v>
       </c>
       <c r="E27" t="n">
-        <v>2604.57</v>
+        <v>286.59</v>
       </c>
       <c r="F27" t="n">
-        <v>37.8</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[9239.28, 1520.59, 2827.86]</t>
+          <t>[3174.28, 2185.42, 8699.01]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[13686.13, 2261.91, 5453.39]</t>
+          <t>[2992.34, 2824.69, 8660.45]</t>
         </is>
       </c>
     </row>
@@ -1414,31 +1414,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3406.05</v>
+        <v>420.91</v>
       </c>
       <c r="E28" t="n">
-        <v>2835.11</v>
+        <v>329.96</v>
       </c>
       <c r="F28" t="n">
-        <v>40.7</v>
+        <v>11.43</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[1570.21, 2924.73, 6420.45]</t>
+          <t>[2178.65, 8654.39, 2637.83]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[2261.91, 5453.39, 11705.42]</t>
+          <t>[2824.69, 8660.45, 2975.6]</t>
         </is>
       </c>
     </row>
@@ -1450,31 +1450,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3495.09</v>
+        <v>389.25</v>
       </c>
       <c r="E29" t="n">
-        <v>3300.31</v>
+        <v>368.83</v>
       </c>
       <c r="F29" t="n">
-        <v>38.28</v>
+        <v>7.34</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[3090.99, 6784.76, 6262.16]</t>
+          <t>[9050.73, 2768.76, 4314.08]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[5453.39, 11705.42, 8880.02]</t>
+          <t>[8660.45, 2975.6, 4823.44]</t>
         </is>
       </c>
     </row>
@@ -1486,31 +1486,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2997.54</v>
+        <v>1416.6</v>
       </c>
       <c r="E30" t="n">
-        <v>2460.26</v>
+        <v>979.8200000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>24.35</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[7080.62, 6561.5, 6320.23]</t>
+          <t>[2840.81, 4438.2, 12182.09]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[11705.42, 8880.02, 5882.78]</t>
+          <t>[2975.6, 4823.44, 14601.52]</t>
         </is>
       </c>
     </row>
@@ -1522,31 +1522,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1376.09</v>
+        <v>1305.98</v>
       </c>
       <c r="E31" t="n">
-        <v>1355.94</v>
+        <v>1042.25</v>
       </c>
       <c r="F31" t="n">
-        <v>16.15</v>
+        <v>15.28</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[7196.13, 7030.97, 11164.63]</t>
+          <t>[4538.99, 12474.48, 2104.03]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[8880.02, 5882.78, 12400.36]</t>
+          <t>[4823.44, 14601.52, 2819.28]</t>
         </is>
       </c>
     </row>
@@ -1558,31 +1558,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>263.82</v>
+        <v>421.01</v>
       </c>
       <c r="E32" t="n">
-        <v>180.97</v>
+        <v>414.97</v>
       </c>
       <c r="F32" t="n">
-        <v>10.71</v>
+        <v>20.78</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[1330.29, 1300.91, 1443.87]</t>
+          <t>[1317.36, 1821.74, 1578.05]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[1377.01, 1753.35, 1487.62]</t>
+          <t>[1640.07, 2317.39, 2004.6]</t>
         </is>
       </c>
     </row>
@@ -1594,31 +1594,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>332.65</v>
+        <v>454.84</v>
       </c>
       <c r="E33" t="n">
-        <v>285.76</v>
+        <v>452.74</v>
       </c>
       <c r="F33" t="n">
-        <v>19.08</v>
+        <v>18.57</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[1289.7, 1431.38, 910.91]</t>
+          <t>[1854.44, 1609.59, 2623.89]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[1753.35, 1487.62, 1248.3]</t>
+          <t>[2317.39, 2004.6, 3124.16]</t>
         </is>
       </c>
     </row>
@@ -1630,31 +1630,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>172.51</v>
+        <v>616.34</v>
       </c>
       <c r="E34" t="n">
-        <v>133.12</v>
+        <v>574.21</v>
       </c>
       <c r="F34" t="n">
-        <v>10.1</v>
+        <v>19.37</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[1515.75, 963.72, 1458.06]</t>
+          <t>[1629.86, 2663.26, 2707.82]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[1487.62, 1248.3, 1544.7]</t>
+          <t>[2004.6, 3124.16, 3594.82]</t>
         </is>
       </c>
     </row>
@@ -1666,31 +1666,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>247.78</v>
+        <v>560.21</v>
       </c>
       <c r="E35" t="n">
-        <v>228.51</v>
+        <v>497.62</v>
       </c>
       <c r="F35" t="n">
-        <v>16.21</v>
+        <v>17.09</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[960.09, 1451.39, 1255.28]</t>
+          <t>[2699.61, 2751.95, 1358.43]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[1248.3, 1544.7, 1559.28]</t>
+          <t>[3124.16, 3594.82, 1583.87]</t>
         </is>
       </c>
     </row>
@@ -1702,31 +1702,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>219.28</v>
+        <v>605.3099999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>198.45</v>
+        <v>549.3</v>
       </c>
       <c r="F36" t="n">
-        <v>16.33</v>
+        <v>22.3</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[1477.75, 1286.04, 685.58]</t>
+          <t>[2791.27, 1381.98, 1378.39]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[1544.7, 1559.28, 940.75]</t>
+          <t>[3594.82, 1583.87, 2020.86]</t>
         </is>
       </c>
     </row>
@@ -1738,31 +1738,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>318.16</v>
+        <v>352.69</v>
       </c>
       <c r="E37" t="n">
-        <v>312.15</v>
+        <v>288.64</v>
       </c>
       <c r="F37" t="n">
-        <v>23.23</v>
+        <v>15.33</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[1279.36, 682.51, 1241.79]</t>
+          <t>[1439.83, 1445.59, 1593.61]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[1559.28, 940.75, 1640.07]</t>
+          <t>[1583.87, 2020.86, 1740.22]</t>
         </is>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>405.09</v>
+        <v>386.48</v>
       </c>
       <c r="E38" t="n">
-        <v>384.02</v>
+        <v>342.66</v>
       </c>
       <c r="F38" t="n">
-        <v>23.74</v>
+        <v>19.59</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[702.06, 1278.79, 1765.3]</t>
+          <t>[1455.94, 1612.98, 1093.28]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[940.75, 1640.07, 2317.39]</t>
+          <t>[2020.86, 1740.22, 1429.08]</t>
         </is>
       </c>
     </row>
@@ -1810,31 +1810,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>421.01</v>
+        <v>157.85</v>
       </c>
       <c r="E39" t="n">
-        <v>414.97</v>
+        <v>111.53</v>
       </c>
       <c r="F39" t="n">
-        <v>20.78</v>
+        <v>7.55</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[1317.36, 1821.74, 1578.05]</t>
+          <t>[1703.25, 1159.65, 1714.54]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[1640.07, 2317.39, 2004.6]</t>
+          <t>[1740.22, 1429.08, 1686.36]</t>
         </is>
       </c>
     </row>
@@ -1846,31 +1846,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>454.84</v>
+        <v>157.79</v>
       </c>
       <c r="E40" t="n">
-        <v>452.74</v>
+        <v>151.69</v>
       </c>
       <c r="F40" t="n">
-        <v>18.57</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[1854.44, 1609.59, 2623.89]</t>
+          <t>[1216.23, 1802.48, 1638.98]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[2317.39, 2004.6, 3124.16]</t>
+          <t>[1429.08, 1686.36, 1765.1]</t>
         </is>
       </c>
     </row>
@@ -1882,31 +1882,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>616.34</v>
+        <v>122.69</v>
       </c>
       <c r="E41" t="n">
-        <v>574.21</v>
+        <v>102.75</v>
       </c>
       <c r="F41" t="n">
-        <v>19.37</v>
+        <v>6.91</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[1629.86, 2663.26, 2707.82]</t>
+          <t>[1883.42, 1717.98, 943.02]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[2004.6, 3124.16, 3594.82]</t>
+          <t>[1686.36, 1765.1, 1007.1]</t>
         </is>
       </c>
     </row>
@@ -1918,31 +1918,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>892.62</v>
+        <v>1211.82</v>
       </c>
       <c r="E42" t="n">
-        <v>882.77</v>
+        <v>1182.3</v>
       </c>
       <c r="F42" t="n">
-        <v>37.04</v>
+        <v>31.68</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[1118.5, 1654.6, 1765.44]</t>
+          <t>[1980.75, 3485.72, 2229.02]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[1822.26, 2673.77, 2690.83]</t>
+          <t>[2845.28, 5000.88, 3396.22]</t>
         </is>
       </c>
     </row>
@@ -1954,31 +1954,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>796.8200000000001</v>
+        <v>1220.87</v>
       </c>
       <c r="E43" t="n">
-        <v>791.6799999999999</v>
+        <v>1214.25</v>
       </c>
       <c r="F43" t="n">
-        <v>31.45</v>
+        <v>28.34</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[1760.45, 1926.36, 1496.92]</t>
+          <t>[3653.32, 2352.94, 3326.91]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[2673.77, 2690.83, 2194.18]</t>
+          <t>[5000.88, 3396.22, 4578.81]</t>
         </is>
       </c>
     </row>
@@ -1990,31 +1990,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>948.23</v>
+        <v>1146.24</v>
       </c>
       <c r="E44" t="n">
-        <v>868.0599999999999</v>
+        <v>1104.69</v>
       </c>
       <c r="F44" t="n">
-        <v>31.95</v>
+        <v>20.22</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[2080.22, 1608.13, 1622.45]</t>
+          <t>[2556.85, 3637.22, 8425.29]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[2690.83, 2194.18, 3029.97]</t>
+          <t>[3396.22, 4578.81, 9958.4]</t>
         </is>
       </c>
     </row>
@@ -2026,31 +2026,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1980.26</v>
+        <v>626.9400000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>1677.58</v>
+        <v>519.75</v>
       </c>
       <c r="F45" t="n">
-        <v>40.99</v>
+        <v>8.48</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[1629.01, 1652.1, 2881.95]</t>
+          <t>[3900.72, 9110.92, 1560.36]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[2194.18, 3029.97, 5971.67]</t>
+          <t>[4578.81, 9958.4, 1594.05]</t>
         </is>
       </c>
     </row>
@@ -2062,31 +2062,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2131.37</v>
+        <v>91.8</v>
       </c>
       <c r="E46" t="n">
-        <v>1997.61</v>
+        <v>89.45</v>
       </c>
       <c r="F46" t="n">
-        <v>46.7</v>
+        <v>3.72</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[1675.56, 2932.63, 1993.99]</t>
+          <t>[9894.03, 1708.93, 2615.82]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[3029.97, 5971.67, 3593.38]</t>
+          <t>[9958.4, 1594.05, 2704.93]</t>
         </is>
       </c>
     </row>
@@ -2098,31 +2098,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1994.23</v>
+        <v>121.42</v>
       </c>
       <c r="E47" t="n">
-        <v>1867</v>
+        <v>101.47</v>
       </c>
       <c r="F47" t="n">
-        <v>44.55</v>
+        <v>5.16</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[3118.72, 2131.09, 1559.5]</t>
+          <t>[1764.37, 2716.18, 2932.77]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[5971.67, 3593.38, 2845.28]</t>
+          <t>[1594.05, 2704.93, 2809.92]</t>
         </is>
       </c>
     </row>
@@ -2134,31 +2134,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1489.16</v>
+        <v>110.11</v>
       </c>
       <c r="E48" t="n">
-        <v>1441.99</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>37.73</v>
+        <v>3.85</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[2347.06, 1728.22, 3038.31]</t>
+          <t>[2678.69, 2888.84, 2376.38]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[3593.38, 2845.28, 5000.88]</t>
+          <t>[2704.93, 2809.92, 2204.76]</t>
         </is>
       </c>
     </row>
@@ -2170,31 +2170,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1211.82</v>
+        <v>155.98</v>
       </c>
       <c r="E49" t="n">
-        <v>1182.3</v>
+        <v>150.74</v>
       </c>
       <c r="F49" t="n">
-        <v>31.68</v>
+        <v>6.01</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[1980.75, 3485.72, 2229.02]</t>
+          <t>[2926.28, 2411.73, 2727.22]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[2845.28, 5000.88, 3396.22]</t>
+          <t>[2809.92, 2204.76, 2856.12]</t>
         </is>
       </c>
     </row>
@@ -2206,31 +2206,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1220.87</v>
+        <v>616.02</v>
       </c>
       <c r="E50" t="n">
-        <v>1214.25</v>
+        <v>454.1</v>
       </c>
       <c r="F50" t="n">
-        <v>28.34</v>
+        <v>10.28</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[3653.32, 2352.94, 3326.91]</t>
+          <t>[2450.73, 2774.85, 5112.41]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[5000.88, 3396.22, 4578.81]</t>
+          <t>[2204.76, 2856.12, 6147.46]</t>
         </is>
       </c>
     </row>
@@ -2242,31 +2242,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1146.24</v>
+        <v>645.99</v>
       </c>
       <c r="E51" t="n">
-        <v>1104.69</v>
+        <v>496.37</v>
       </c>
       <c r="F51" t="n">
-        <v>20.22</v>
+        <v>9.83</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[2556.85, 3637.22, 8425.29]</t>
+          <t>[2757.85, 5081.2, 3399.35]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[3396.22, 4578.81, 9958.4]</t>
+          <t>[2856.12, 6147.46, 3723.94]</t>
         </is>
       </c>
     </row>
@@ -2278,31 +2278,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3.12</v>
+        <v>7.37</v>
       </c>
       <c r="E52" t="n">
-        <v>2.6</v>
+        <v>5.97</v>
       </c>
       <c r="F52" t="n">
-        <v>85.81999999999999</v>
+        <v>95.34</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[0.1, 0.09, 0.21]</t>
+          <t>[0.0, 0.47, 0.41]</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[0.3, 4.3, 3.6]</t>
+          <t>[2.3, 12.5, 4.0]</t>
         </is>
       </c>
     </row>
@@ -2314,31 +2314,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3.6</v>
+        <v>7.48</v>
       </c>
       <c r="E53" t="n">
-        <v>3.57</v>
+        <v>6.43</v>
       </c>
       <c r="F53" t="n">
-        <v>92.77</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[0.1, 0.26, 0.44]</t>
+          <t>[0.67, 0.66, 1.77]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[4.3, 3.6, 3.6]</t>
+          <t>[12.5, 4.0, 5.9]</t>
         </is>
       </c>
     </row>
@@ -2350,31 +2350,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3.03</v>
+        <v>10.79</v>
       </c>
       <c r="E54" t="n">
-        <v>3.01</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>92.39</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[0.27, 0.39, 0.11]</t>
+          <t>[0.47, 1.27, 1.03]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[3.6, 3.6, 2.6]</t>
+          <t>[4.0, 5.9, 18.8]</t>
         </is>
       </c>
     </row>
@@ -2386,31 +2386,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.6</v>
+        <v>9.92</v>
       </c>
       <c r="E55" t="n">
-        <v>2.55</v>
+        <v>7.39</v>
       </c>
       <c r="F55" t="n">
-        <v>89.92</v>
+        <v>78</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[0.4, 0.11, 0.34]</t>
+          <t>[2.44, 2.09, 0.31]</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[3.6, 2.6, 2.3]</t>
+          <t>[5.9, 18.8, 2.3]</t>
         </is>
       </c>
     </row>
@@ -2422,31 +2422,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1.84</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>1.58</v>
+        <v>6.88</v>
       </c>
       <c r="F56" t="n">
-        <v>91.44</v>
+        <v>86.2</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[0.11, 0.33, 0.02]</t>
+          <t>[2.36, 0.35, 0.35]</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[2.6, 2.3, 0.3]</t>
+          <t>[18.8, 2.3, 2.6]</t>
         </is>
       </c>
     </row>
@@ -2458,31 +2458,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="E57" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="F57" t="n">
-        <v>83.39</v>
+        <v>74.14</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[0.72, 0.06, 0.0]</t>
+          <t>[0.18, 0.18, 0.41]</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[2.3, 0.3, 2.3]</t>
+          <t>[2.3, 2.6, 0.3]</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,33 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>7.05</v>
+        <v>1.44</v>
       </c>
       <c r="E58" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="F58" t="n">
-        <v>93.93000000000001</v>
+        <v>1.17</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[0.04, 0.0, 0.51]</t>
+          <t>[0.28, 0.63, 0.87]</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[0.3, 2.3, 12.5]</t>
+          <t>[2.6, 0.3, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2530,31 +2532,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>7.37</v>
+        <v>0.63</v>
       </c>
       <c r="E59" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="F59" t="n">
-        <v>95.34</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[0.0, 0.47, 0.41]</t>
+          <t>[0.71, 0.97, 0.3]</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[2.3, 12.5, 4.0]</t>
+          <t>[0.3, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2566,31 +2570,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7.48</v>
+        <v>26.01</v>
       </c>
       <c r="E60" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F60" t="n">
-        <v>82.70999999999999</v>
+        <v>15.23</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[0.67, 0.66, 1.77]</t>
+          <t>[0.49, 0.16, 0.45]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[12.5, 4.0, 5.9]</t>
+          <t>[0.0, 0.0, 45.5]</t>
         </is>
       </c>
     </row>
@@ -2602,31 +2608,33 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.79</v>
+        <v>36.2</v>
       </c>
       <c r="E61" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="F61" t="n">
-        <v>87.06999999999999</v>
+        <v>29.61</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[0.47, 1.27, 1.03]</t>
+          <t>[0.16, 0.41, 0.03]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[4.0, 5.9, 18.8]</t>
+          <t>[0.0, 45.5, 43.6]</t>
         </is>
       </c>
     </row>
@@ -2638,31 +2646,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="E62" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="F62" t="n">
-        <v>8.69</v>
+        <v>14.77</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[2.32, 3.81, 3.92]</t>
+          <t>[2.23, 3.36, 2.91]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[2.2, 3.5, 3.5]</t>
+          <t>[1.7, 3.4, 2.6]</t>
         </is>
       </c>
     </row>
@@ -2674,31 +2682,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="E63" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="F63" t="n">
-        <v>15.67</v>
+        <v>17.71</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[3.75, 3.85, 3.51]</t>
+          <t>[3.33, 2.88, 2.8]</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[3.5, 3.5, 2.7]</t>
+          <t>[3.4, 2.6, 2.0]</t>
         </is>
       </c>
     </row>
@@ -2710,31 +2718,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="E64" t="n">
         <v>0.58</v>
       </c>
       <c r="F64" t="n">
-        <v>22.85</v>
+        <v>22.84</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[3.84, 3.5, 2.71]</t>
+          <t>[2.86, 2.79, 2.91]</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[3.5, 2.7, 2.1]</t>
+          <t>[2.6, 2.0, 3.6]</t>
         </is>
       </c>
     </row>
@@ -2746,31 +2754,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.76</v>
+        <v>0.6</v>
       </c>
       <c r="E65" t="n">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="F65" t="n">
-        <v>29.59</v>
+        <v>22.9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[3.45, 2.68, 3.6]</t>
+          <t>[2.79, 2.94, 1.89]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[2.7, 2.1, 2.7]</t>
+          <t>[2.0, 3.6, 1.7]</t>
         </is>
       </c>
     </row>
@@ -2782,31 +2790,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.99</v>
+        <v>0.43</v>
       </c>
       <c r="E66" t="n">
-        <v>0.95</v>
+        <v>0.36</v>
       </c>
       <c r="F66" t="n">
-        <v>46.44</v>
+        <v>12.64</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[2.69, 3.66, 2.99]</t>
+          <t>[2.93, 1.87, 2.96]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[2.1, 2.7, 1.7]</t>
+          <t>[3.6, 1.7, 2.7]</t>
         </is>
       </c>
     </row>
@@ -2818,31 +2826,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.98</v>
+        <v>0.27</v>
       </c>
       <c r="E67" t="n">
-        <v>0.93</v>
+        <v>0.26</v>
       </c>
       <c r="F67" t="n">
-        <v>47.91</v>
+        <v>10.98</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[3.66, 2.97, 2.27]</t>
+          <t>[1.88, 2.96, 3.04]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[2.7, 1.7, 1.7]</t>
+          <t>[1.7, 2.7, 2.7]</t>
         </is>
       </c>
     </row>
@@ -2854,31 +2862,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="E68" t="n">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="F68" t="n">
-        <v>36.55</v>
+        <v>19.31</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[2.98, 2.27, 3.42]</t>
+          <t>[2.96, 3.04, 2.72]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[1.7, 1.7, 3.4]</t>
+          <t>[2.7, 2.7, 2.0]</t>
         </is>
       </c>
     </row>
@@ -2890,31 +2898,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="E69" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="F69" t="n">
-        <v>14.77</v>
+        <v>16.2</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[2.23, 3.36, 2.91]</t>
+          <t>[3.04, 2.72, 2.1]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[1.7, 3.4, 2.6]</t>
+          <t>[2.7, 2.0, 2.1]</t>
         </is>
       </c>
     </row>
@@ -2926,31 +2934,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="E70" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="F70" t="n">
-        <v>17.71</v>
+        <v>15.83</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[3.33, 2.88, 2.8]</t>
+          <t>[2.73, 2.11, 2.87]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[3.4, 2.6, 2.0]</t>
+          <t>[2.0, 2.1, 2.6]</t>
         </is>
       </c>
     </row>
@@ -2962,31 +2970,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.62</v>
+        <v>0.34</v>
       </c>
       <c r="E71" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="F71" t="n">
-        <v>22.84</v>
+        <v>13.74</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[2.86, 2.79, 2.91]</t>
+          <t>[2.08, 2.84, 2.23]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[2.6, 2.0, 3.6]</t>
+          <t>[2.1, 2.6, 1.7]</t>
         </is>
       </c>
     </row>
@@ -2998,31 +3006,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>262.88</v>
+        <v>103.12</v>
       </c>
       <c r="E72" t="n">
-        <v>260.26</v>
+        <v>94.14</v>
       </c>
       <c r="F72" t="n">
-        <v>42</v>
+        <v>23.21</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[459.63, 376.03, 263.37]</t>
+          <t>[426.7, 294.2, 313.72]</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[767.55, 593.84, 518.43]</t>
+          <t>[352.82, 350.02, 466.45]</t>
         </is>
       </c>
     </row>
@@ -3034,31 +3042,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>191.09</v>
+        <v>173.44</v>
       </c>
       <c r="E73" t="n">
-        <v>178.67</v>
+        <v>154.01</v>
       </c>
       <c r="F73" t="n">
-        <v>32.67</v>
+        <v>33.34</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[379.55, 280.53, 606.95]</t>
+          <t>[294.28, 311.25, 242.95]</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[593.84, 518.43, 523.12]</t>
+          <t>[350.02, 466.45, 494.05]</t>
         </is>
       </c>
     </row>
@@ -3070,31 +3078,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>289.99</v>
+        <v>172.75</v>
       </c>
       <c r="E74" t="n">
-        <v>258.77</v>
+        <v>152.25</v>
       </c>
       <c r="F74" t="n">
-        <v>56.39</v>
+        <v>30.29</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[302.26, 647.19, 856.4]</t>
+          <t>[311.0, 243.48, 693.81]</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[518.43, 523.12, 420.32]</t>
+          <t>[466.45, 494.05, 744.54]</t>
         </is>
       </c>
     </row>
@@ -3106,31 +3114,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>496.37</v>
+        <v>208.87</v>
       </c>
       <c r="E75" t="n">
-        <v>430.9</v>
+        <v>184.43</v>
       </c>
       <c r="F75" t="n">
-        <v>87.41</v>
+        <v>31.88</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[645.88, 864.37, 1271.11]</t>
+          <t>[242.27, 698.75, 407.9]</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[523.12, 420.32, 545.23]</t>
+          <t>[494.05, 744.54, 663.61]</t>
         </is>
       </c>
     </row>
@@ -3142,31 +3150,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>498.77</v>
+        <v>179.49</v>
       </c>
       <c r="E76" t="n">
-        <v>411.15</v>
+        <v>158.46</v>
       </c>
       <c r="F76" t="n">
-        <v>84.90000000000001</v>
+        <v>24.22</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[870.94, 1280.78, 422.93]</t>
+          <t>[698.95, 415.44, 441.95]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[420.32, 545.23, 375.66]</t>
+          <t>[744.54, 663.61, 623.57]</t>
         </is>
       </c>
     </row>
@@ -3178,31 +3186,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>427.56</v>
+        <v>180.22</v>
       </c>
       <c r="E77" t="n">
-        <v>287.35</v>
+        <v>160.84</v>
       </c>
       <c r="F77" t="n">
-        <v>56.71</v>
+        <v>26.56</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[1279.68, 418.5, 437.6]</t>
+          <t>[415.12, 442.12, 347.8]</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[545.23, 375.66, 352.82]</t>
+          <t>[663.61, 623.57, 400.39]</t>
         </is>
       </c>
     </row>
@@ -3214,31 +3222,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>60.26</v>
+        <v>161.53</v>
       </c>
       <c r="E78" t="n">
-        <v>58.43</v>
+        <v>145.05</v>
       </c>
       <c r="F78" t="n">
-        <v>16.36</v>
+        <v>30.57</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[418.09, 430.82, 295.16]</t>
+          <t>[437.89, 355.29, 607.75]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[375.66, 352.82, 350.02]</t>
+          <t>[623.57, 400.39, 403.4]</t>
         </is>
       </c>
     </row>
@@ -3250,31 +3258,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>103.12</v>
+        <v>169.81</v>
       </c>
       <c r="E79" t="n">
-        <v>94.14</v>
+        <v>150.65</v>
       </c>
       <c r="F79" t="n">
-        <v>23.21</v>
+        <v>36.16</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[426.7, 294.2, 313.72]</t>
+          <t>[360.06, 618.15, 632.62]</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[352.82, 350.02, 466.45]</t>
+          <t>[400.39, 403.4, 435.75]</t>
         </is>
       </c>
     </row>
@@ -3286,31 +3294,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>173.44</v>
+        <v>265.3</v>
       </c>
       <c r="E80" t="n">
-        <v>154.01</v>
+        <v>256.5</v>
       </c>
       <c r="F80" t="n">
-        <v>33.34</v>
+        <v>55.94</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[294.28, 311.25, 242.95]</t>
+          <t>[621.09, 635.75, 869.51]</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[350.02, 466.45, 494.05]</t>
+          <t>[403.4, 435.75, 517.7]</t>
         </is>
       </c>
     </row>
@@ -3322,31 +3330,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>172.75</v>
+        <v>225.64</v>
       </c>
       <c r="E81" t="n">
-        <v>152.25</v>
+        <v>189.6</v>
       </c>
       <c r="F81" t="n">
-        <v>30.29</v>
+        <v>39.85</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[311.0, 243.48, 693.81]</t>
+          <t>[626.04, 856.79, 419.33]</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[466.45, 494.05, 744.54]</t>
+          <t>[435.75, 517.7, 379.9]</t>
         </is>
       </c>
     </row>
@@ -3358,31 +3366,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>959.29</v>
+        <v>123.81</v>
       </c>
       <c r="E82" t="n">
-        <v>752.54</v>
+        <v>120.92</v>
       </c>
       <c r="F82" t="n">
-        <v>20.88</v>
+        <v>3.1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[2763.93, 2820.7, 2511.27]</t>
+          <t>[4574.75, 4388.98, 3266.54]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[2452.32, 3173.15, 4104.82]</t>
+          <t>[4488.08, 4264.39, 3418.05]</t>
         </is>
       </c>
     </row>
@@ -3394,31 +3402,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>991.87</v>
+        <v>274.05</v>
       </c>
       <c r="E83" t="n">
-        <v>780.15</v>
+        <v>235.32</v>
       </c>
       <c r="F83" t="n">
-        <v>20.61</v>
+        <v>4.98</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[2782.57, 2459.85, 2926.62]</t>
+          <t>[4377.59, 3257.34, 6140.56]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[3173.15, 4104.82, 3231.51]</t>
+          <t>[4264.39, 3418.05, 5708.5]</t>
         </is>
       </c>
     </row>
@@ -3430,31 +3438,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>983.6799999999999</v>
+        <v>2749.7</v>
       </c>
       <c r="E84" t="n">
-        <v>783</v>
+        <v>1773.56</v>
       </c>
       <c r="F84" t="n">
-        <v>20.72</v>
+        <v>14.31</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[2493.43, 2993.63, 2715.51]</t>
+          <t>[3257.64, 6127.3, 10609.3]</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[4104.82, 3231.51, 3215.25]</t>
+          <t>[3418.05, 5708.5, 15350.76]</t>
         </is>
       </c>
     </row>
@@ -3466,31 +3474,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>234.11</v>
+        <v>2739.69</v>
       </c>
       <c r="E85" t="n">
-        <v>192.3</v>
+        <v>1769.77</v>
       </c>
       <c r="F85" t="n">
-        <v>5.79</v>
+        <v>15.02</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[3098.31, 2838.1, 4285.47]</t>
+          <t>[6128.98, 10627.02, 2551.52]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[3231.51, 3215.25, 4352.03]</t>
+          <t>[5708.5, 15350.76, 2386.42]</t>
         </is>
       </c>
     </row>
@@ -3502,31 +3510,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>273.26</v>
+        <v>2758.27</v>
       </c>
       <c r="E86" t="n">
-        <v>240</v>
+        <v>1802.99</v>
       </c>
       <c r="F86" t="n">
-        <v>8.220000000000001</v>
+        <v>17.81</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[2846.71, 4291.27, 2170.59]</t>
+          <t>[10602.54, 2543.12, 2659.25]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[3215.25, 4352.03, 2461.28]</t>
+          <t>[15350.76, 2386.42, 3163.3]</t>
         </is>
       </c>
     </row>
@@ -3538,31 +3546,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>156.13</v>
+        <v>275.79</v>
       </c>
       <c r="E87" t="n">
-        <v>111.84</v>
+        <v>218.07</v>
       </c>
       <c r="F87" t="n">
-        <v>4.12</v>
+        <v>7.65</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[4332.69, 2196.48, 4539.45]</t>
+          <t>[2601.42, 2736.93, 2702.17]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[4352.03, 2461.28, 4488.08]</t>
+          <t>[2386.42, 3163.3, 2715.0]</t>
         </is>
       </c>
     </row>
@@ -3574,31 +3582,31 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>162.64</v>
+        <v>356.39</v>
       </c>
       <c r="E88" t="n">
-        <v>136.8</v>
+        <v>302.89</v>
       </c>
       <c r="F88" t="n">
-        <v>4.67</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[2202.39, 4543.12, 4360.84]</t>
+          <t>[2710.52, 2676.92, 2827.22]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[2461.28, 4488.08, 4264.39]</t>
+          <t>[3163.3, 2715.0, 3245.04]</t>
         </is>
       </c>
     </row>
@@ -3610,31 +3618,31 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>123.81</v>
+        <v>517.15</v>
       </c>
       <c r="E89" t="n">
-        <v>120.92</v>
+        <v>400.62</v>
       </c>
       <c r="F89" t="n">
-        <v>3.1</v>
+        <v>11.84</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[4574.75, 4388.98, 3266.54]</t>
+          <t>[2705.74, 2862.15, 2654.58]</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[4488.08, 4264.39, 3418.05]</t>
+          <t>[2715.0, 3245.04, 3464.3]</t>
         </is>
       </c>
     </row>
@@ -3646,31 +3654,31 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>274.05</v>
+        <v>1463.55</v>
       </c>
       <c r="E90" t="n">
-        <v>235.32</v>
+        <v>1184.41</v>
       </c>
       <c r="F90" t="n">
-        <v>4.98</v>
+        <v>23.86</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[4377.59, 3257.34, 6140.56]</t>
+          <t>[2868.66, 2662.7, 4073.74]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[4264.39, 3418.05, 5708.5]</t>
+          <t>[3245.04, 3464.3, 6448.97]</t>
         </is>
       </c>
     </row>
@@ -3682,31 +3690,31 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2749.7</v>
+        <v>1421.87</v>
       </c>
       <c r="E91" t="n">
-        <v>1773.56</v>
+        <v>1135.38</v>
       </c>
       <c r="F91" t="n">
-        <v>14.31</v>
+        <v>23.77</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[3257.64, 6127.3, 10609.3]</t>
+          <t>[2691.65, 4132.09, 2103.0]</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>[3418.05, 5708.5, 15350.76]</t>
+          <t>[3464.3, 6448.97, 2419.61]</t>
         </is>
       </c>
     </row>
@@ -3718,31 +3726,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>122.29</v>
+        <v>387.39</v>
       </c>
       <c r="E92" t="n">
-        <v>96.29000000000001</v>
+        <v>298.03</v>
       </c>
       <c r="F92" t="n">
-        <v>2.44</v>
+        <v>7.16</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[2747.89, 3397.43, 4375.72]</t>
+          <t>[3242.51, 5690.97, 3624.89]</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[2800.48, 3363.48, 4578.07]</t>
+          <t>[3873.69, 5466.61, 3586.35]</t>
         </is>
       </c>
     </row>
@@ -3754,31 +3762,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>276.87</v>
+        <v>178.02</v>
       </c>
       <c r="E93" t="n">
-        <v>222.86</v>
+        <v>157.14</v>
       </c>
       <c r="F93" t="n">
-        <v>5.44</v>
+        <v>3.25</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[3400.37, 4382.83, 3547.89]</t>
+          <t>[5736.95, 3657.09, 4447.71]</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>[3363.48, 4578.07, 3984.34]</t>
+          <t>[5466.61, 3586.35, 4578.05]</t>
         </is>
       </c>
     </row>
@@ -3790,31 +3798,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>308.22</v>
+        <v>91.05</v>
       </c>
       <c r="E94" t="n">
-        <v>284.75</v>
+        <v>75.22</v>
       </c>
       <c r="F94" t="n">
-        <v>6.83</v>
+        <v>1.7</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[4366.12, 3533.18, 4025.66]</t>
+          <t>[3648.87, 4434.62, 8980.66]</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[4578.07, 3984.34, 4216.8]</t>
+          <t>[3586.35, 4578.05, 9000.38]</t>
         </is>
       </c>
     </row>
@@ -3826,31 +3834,31 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>277.38</v>
+        <v>125.9</v>
       </c>
       <c r="E95" t="n">
-        <v>233.02</v>
+        <v>110.92</v>
       </c>
       <c r="F95" t="n">
-        <v>5.41</v>
+        <v>3.24</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[3544.82, 4042.6, 7812.2]</t>
+          <t>[4434.95, 8972.96, 2744.51]</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[3984.34, 4216.8, 7897.55]</t>
+          <t>[4578.05, 9000.38, 2582.26]</t>
         </is>
       </c>
     </row>
@@ -3862,31 +3870,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>217.35</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="E96" t="n">
-        <v>166.46</v>
+        <v>68.83</v>
       </c>
       <c r="F96" t="n">
-        <v>4.85</v>
+        <v>2.5</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[4088.08, 7914.86, 2779.79]</t>
+          <t>[9008.37, 2752.37, 3471.83]</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[4216.8, 7897.55, 3133.14]</t>
+          <t>[9000.38, 2582.26, 3443.42]</t>
         </is>
       </c>
     </row>
@@ -3898,31 +3906,31 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>431.94</v>
+        <v>193.03</v>
       </c>
       <c r="E97" t="n">
-        <v>350.11</v>
+        <v>166.1</v>
       </c>
       <c r="F97" t="n">
-        <v>9.550000000000001</v>
+        <v>4.61</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[7940.94, 2789.19, 3210.71]</t>
+          <t>[2760.82, 3483.34, 4583.69]</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[7897.55, 3133.14, 3873.69]</t>
+          <t>[2582.26, 3443.42, 4863.53]</t>
         </is>
       </c>
     </row>
@@ -3934,31 +3942,31 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>439.27</v>
+        <v>225.61</v>
       </c>
       <c r="E98" t="n">
-        <v>387.24</v>
+        <v>189.51</v>
       </c>
       <c r="F98" t="n">
-        <v>10.29</v>
+        <v>4.31</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[2792.45, 3212.41, 5626.35]</t>
+          <t>[3465.66, 4551.8, 3765.41]</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>[3133.14, 3873.69, 5466.61]</t>
+          <t>[3443.42, 4863.53, 3999.99]</t>
         </is>
       </c>
     </row>
@@ -3970,31 +3978,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>387.39</v>
+        <v>223.11</v>
       </c>
       <c r="E99" t="n">
-        <v>298.03</v>
+        <v>184.33</v>
       </c>
       <c r="F99" t="n">
-        <v>7.16</v>
+        <v>4.15</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[3242.51, 5690.97, 3624.89]</t>
+          <t>[4554.69, 3768.04, 4219.64]</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>[3873.69, 5466.61, 3586.35]</t>
+          <t>[4863.53, 3999.99, 4231.86]</t>
         </is>
       </c>
     </row>
@@ -4006,31 +4014,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>178.02</v>
+        <v>110.87</v>
       </c>
       <c r="E100" t="n">
-        <v>157.14</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="F100" t="n">
-        <v>3.25</v>
+        <v>1.99</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[5736.95, 3657.09, 4447.71]</t>
+          <t>[3814.65, 4274.69, 8262.05]</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>[5466.61, 3586.35, 4578.05]</t>
+          <t>[3999.99, 4231.86, 8235.66]</t>
         </is>
       </c>
     </row>
@@ -4042,31 +4050,31 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>91.05</v>
+        <v>418.92</v>
       </c>
       <c r="E101" t="n">
-        <v>75.22</v>
+        <v>289.8</v>
       </c>
       <c r="F101" t="n">
-        <v>1.7</v>
+        <v>7.25</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[3648.87, 4434.62, 8980.66]</t>
+          <t>[4302.0, 8317.36, 3036.4]</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[3586.35, 4578.05, 9000.38]</t>
+          <t>[4231.86, 8235.66, 3753.95]</t>
         </is>
       </c>
     </row>
@@ -4078,31 +4086,31 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>298.69</v>
+        <v>929.11</v>
       </c>
       <c r="E102" t="n">
-        <v>248.15</v>
+        <v>882.46</v>
       </c>
       <c r="F102" t="n">
-        <v>11.68</v>
+        <v>23.13</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[2319.35, 1511.96, 1848.98]</t>
+          <t>[2367.77, 4584.79, 2003.2]</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[2230.16, 1689.58, 2326.63]</t>
+          <t>[3097.3, 5874.2, 2631.65]</t>
         </is>
       </c>
     </row>
@@ -4114,31 +4122,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>451.82</v>
+        <v>1112.56</v>
       </c>
       <c r="E103" t="n">
-        <v>420.99</v>
+        <v>1058.96</v>
       </c>
       <c r="F103" t="n">
-        <v>22.15</v>
+        <v>25.05</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[1497.39, 1824.37, 1129.43]</t>
+          <t>[4664.2, 2045.07, 2899.81]</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>[1689.58, 2326.63, 1697.95]</t>
+          <t>[5874.2, 2631.65, 4280.1]</t>
         </is>
       </c>
     </row>
@@ -4150,31 +4158,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>438.49</v>
+        <v>1049.83</v>
       </c>
       <c r="E104" t="n">
-        <v>421.07</v>
+        <v>992.58</v>
       </c>
       <c r="F104" t="n">
-        <v>21.24</v>
+        <v>22.03</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>[1863.29, 1152.67, 1924.98]</t>
+          <t>[2121.99, 3024.24, 5760.11]</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>[2326.63, 1697.95, 2179.57]</t>
+          <t>[2631.65, 4280.1, 6972.33]</t>
         </is>
       </c>
     </row>
@@ -4186,31 +4194,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1075.17</v>
+        <v>844.21</v>
       </c>
       <c r="E105" t="n">
-        <v>836.92</v>
+        <v>728.41</v>
       </c>
       <c r="F105" t="n">
-        <v>22.37</v>
+        <v>15.18</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>[1173.16, 1967.77, 4927.26]</t>
+          <t>[3157.88, 6044.79, 2386.47]</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>[1697.95, 2179.57, 6701.44]</t>
+          <t>[4280.1, 6972.33, 2251.02]</t>
         </is>
       </c>
     </row>
@@ -4222,31 +4230,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>992.26</v>
+        <v>372.01</v>
       </c>
       <c r="E106" t="n">
-        <v>810.24</v>
+        <v>294.08</v>
       </c>
       <c r="F106" t="n">
-        <v>21.35</v>
+        <v>7.39</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>[2053.78, 5173.77, 1413.04]</t>
+          <t>[6398.29, 2543.25, 1671.3]</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>[2179.57, 6701.44, 2190.31]</t>
+          <t>[6972.33, 2251.02, 1655.31]</t>
         </is>
       </c>
     </row>
@@ -4258,31 +4266,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1111.24</v>
+        <v>271.27</v>
       </c>
       <c r="E107" t="n">
-        <v>1060.9</v>
+        <v>242.06</v>
       </c>
       <c r="F107" t="n">
-        <v>28.89</v>
+        <v>11</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>[5176.77, 1413.12, 2216.46]</t>
+          <t>[2640.23, 1744.73, 2156.7]</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>[6701.44, 2190.31, 3097.3]</t>
+          <t>[2251.02, 1655.31, 2404.24]</t>
         </is>
       </c>
     </row>
@@ -4294,31 +4302,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1081.73</v>
+        <v>291.13</v>
       </c>
       <c r="E108" t="n">
-        <v>1028.83</v>
+        <v>251.89</v>
       </c>
       <c r="F108" t="n">
-        <v>28.94</v>
+        <v>12.76</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>[1438.84, 2261.13, 4375.36]</t>
+          <t>[1712.1, 2113.21, 1384.89]</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>[2190.31, 3097.3, 5874.2]</t>
+          <t>[1655.31, 2404.24, 1792.75]</t>
         </is>
       </c>
     </row>
@@ -4330,31 +4338,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>929.11</v>
+        <v>261.77</v>
       </c>
       <c r="E109" t="n">
-        <v>882.46</v>
+        <v>211.32</v>
       </c>
       <c r="F109" t="n">
-        <v>23.13</v>
+        <v>10.59</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>[2367.77, 4584.79, 2003.2]</t>
+          <t>[2154.95, 1414.08, 2196.71]</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>[3097.3, 5874.2, 2631.65]</t>
+          <t>[2404.24, 1792.75, 2202.71]</t>
         </is>
       </c>
     </row>
@@ -4366,31 +4374,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1112.56</v>
+        <v>488.33</v>
       </c>
       <c r="E110" t="n">
-        <v>1058.96</v>
+        <v>395.13</v>
       </c>
       <c r="F110" t="n">
-        <v>25.05</v>
+        <v>11.04</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>[4664.2, 2045.07, 2899.81]</t>
+          <t>[1468.53, 2287.25, 6168.64]</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>[5874.2, 2631.65, 4280.1]</t>
+          <t>[1792.75, 2202.71, 6945.26]</t>
         </is>
       </c>
     </row>
@@ -4402,31 +4410,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1049.83</v>
+        <v>347.71</v>
       </c>
       <c r="E111" t="n">
-        <v>992.58</v>
+        <v>318.75</v>
       </c>
       <c r="F111" t="n">
-        <v>22.03</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>[2121.99, 3024.24, 5760.11]</t>
+          <t>[2380.69, 6437.42, 1855.15]</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>[2631.65, 4280.1, 6972.33]</t>
+          <t>[2202.71, 6945.26, 2125.57]</t>
         </is>
       </c>
     </row>
@@ -4438,31 +4446,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>481.4</v>
+        <v>494.86</v>
       </c>
       <c r="E112" t="n">
-        <v>455.53</v>
+        <v>446.63</v>
       </c>
       <c r="F112" t="n">
-        <v>13.19</v>
+        <v>18.75</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>[2591.75, 3597.11, 2685.2]</t>
+          <t>[2238.96, 3269.66, 1221.98]</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>[2833.58, 4113.6, 3293.47]</t>
+          <t>[2421.12, 3723.42, 1925.96]</t>
         </is>
       </c>
     </row>
@@ -4474,31 +4482,31 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>490</v>
+        <v>483.67</v>
       </c>
       <c r="E113" t="n">
-        <v>486.21</v>
+        <v>434.94</v>
       </c>
       <c r="F113" t="n">
-        <v>13.94</v>
+        <v>19.64</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>[3636.13, 2728.83, 2769.15]</t>
+          <t>[3289.92, 1231.18, 1399.38]</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>[4113.6, 3293.47, 3185.67]</t>
+          <t>[3723.42, 1925.96, 1575.93]</t>
         </is>
       </c>
     </row>
@@ -4510,31 +4518,31 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>406.8</v>
+        <v>405.78</v>
       </c>
       <c r="E114" t="n">
-        <v>399.11</v>
+        <v>313.24</v>
       </c>
       <c r="F114" t="n">
-        <v>11.56</v>
+        <v>16.47</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>[2784.38, 2826.58, 3809.87]</t>
+          <t>[1248.87, 1421.73, 2320.74]</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>[3293.47, 3185.67, 4139.04]</t>
+          <t>[1925.96, 1575.93, 2429.17]</t>
         </is>
       </c>
     </row>
@@ -4546,31 +4554,31 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2448.61</v>
+        <v>95.5</v>
       </c>
       <c r="E115" t="n">
-        <v>1617.38</v>
+        <v>78.23</v>
       </c>
       <c r="F115" t="n">
-        <v>21.99</v>
+        <v>3.59</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>[2848.74, 3841.03, 4535.72]</t>
+          <t>[1483.71, 2434.42, 2785.0]</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>[3185.67, 4139.04, 8752.92]</t>
+          <t>[1575.93, 2429.17, 2922.22]</t>
         </is>
       </c>
     </row>
@@ -4582,31 +4590,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2452.63</v>
+        <v>132.94</v>
       </c>
       <c r="E116" t="n">
-        <v>1738.93</v>
+        <v>113.09</v>
       </c>
       <c r="F116" t="n">
-        <v>31.59</v>
+        <v>3.33</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>[3858.84, 4584.21, 1134.3]</t>
+          <t>[2462.49, 2819.78, 3784.62]</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>[4139.04, 8752.92, 1902.17]</t>
+          <t>[2429.17, 2922.22, 3988.12]</t>
         </is>
       </c>
     </row>
@@ -4618,31 +4626,31 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2451.55</v>
+        <v>53.43</v>
       </c>
       <c r="E117" t="n">
-        <v>1754.73</v>
+        <v>45.02</v>
       </c>
       <c r="F117" t="n">
-        <v>33.88</v>
+        <v>1.31</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>[4589.65, 1137.79, 2084.57]</t>
+          <t>[2916.85, 3931.23, 3065.04]</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>[8752.92, 1902.17, 2421.12]</t>
+          <t>[2922.22, 3988.12, 3137.83]</t>
         </is>
       </c>
     </row>
@@ -4654,31 +4662,31 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>534.17</v>
+        <v>112.38</v>
       </c>
       <c r="E118" t="n">
-        <v>496.13</v>
+        <v>112.22</v>
       </c>
       <c r="F118" t="n">
-        <v>20.58</v>
+        <v>3.31</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>[1187.77, 2185.94, 3184.6]</t>
+          <t>[3875.71, 3018.37, 3079.61]</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>[1902.17, 2421.12, 3723.42]</t>
+          <t>[3988.12, 3137.83, 3184.39]</t>
         </is>
       </c>
     </row>
@@ -4690,31 +4698,31 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>494.86</v>
+        <v>138.3</v>
       </c>
       <c r="E119" t="n">
-        <v>446.63</v>
+        <v>109.25</v>
       </c>
       <c r="F119" t="n">
-        <v>18.75</v>
+        <v>2.89</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>[2238.96, 3269.66, 1221.98]</t>
+          <t>[3078.12, 3144.96, 4357.13]</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>[2421.12, 3723.42, 1925.96]</t>
+          <t>[3137.83, 3184.39, 4128.53]</t>
         </is>
       </c>
     </row>
@@ -4726,31 +4734,31 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>483.67</v>
+        <v>763.38</v>
       </c>
       <c r="E120" t="n">
-        <v>434.94</v>
+        <v>544.04</v>
       </c>
       <c r="F120" t="n">
-        <v>19.64</v>
+        <v>12.95</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[3289.92, 1231.18, 1399.38]</t>
+          <t>[3210.78, 4452.65, 5529.72]</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>[3723.42, 1925.96, 1575.93]</t>
+          <t>[3184.39, 4128.53, 4248.12]</t>
         </is>
       </c>
     </row>
@@ -4762,31 +4770,31 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>405.78</v>
+        <v>815.53</v>
       </c>
       <c r="E121" t="n">
-        <v>313.24</v>
+        <v>628.8200000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>16.47</v>
+        <v>17.01</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>[1248.87, 1421.73, 2320.74]</t>
+          <t>[4506.56, 5600.12, 1399.44]</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>[1925.96, 1575.93, 2429.17]</t>
+          <t>[4128.53, 4248.12, 1555.87]</t>
         </is>
       </c>
     </row>
@@ -4798,31 +4806,31 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>41.56</v>
+        <v>144.92</v>
       </c>
       <c r="E122" t="n">
-        <v>39.37</v>
+        <v>144.89</v>
       </c>
       <c r="F122" t="n">
-        <v>3.53</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>[1362.24, 1089.86, 1122.31]</t>
+          <t>[1432.82, 1582.99, 1775.3]</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>[1389.65, 1031.91, 1089.57]</t>
+          <t>[1581.37, 1724.95, 1919.48]</t>
         </is>
       </c>
     </row>
@@ -4834,31 +4842,31 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>37.81</v>
+        <v>133.62</v>
       </c>
       <c r="E123" t="n">
-        <v>34.25</v>
+        <v>133.32</v>
       </c>
       <c r="F123" t="n">
-        <v>3.14</v>
+        <v>7.31</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>[1088.11, 1117.68, 1318.5]</t>
+          <t>[1598.14, 1792.27, 1692.53]</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>[1031.91, 1089.57, 1336.93]</t>
+          <t>[1724.95, 1919.48, 1838.46]</t>
         </is>
       </c>
     </row>
@@ -4870,31 +4878,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>69.06999999999999</v>
+        <v>322.45</v>
       </c>
       <c r="E124" t="n">
-        <v>54.47</v>
+        <v>260.64</v>
       </c>
       <c r="F124" t="n">
-        <v>4.32</v>
+        <v>12.21</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>[1106.61, 1304.42, 1155.21]</t>
+          <t>[1801.22, 1703.75, 1756.16]</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>[1089.57, 1336.93, 1269.08]</t>
+          <t>[1919.48, 1838.46, 2285.11]</t>
         </is>
       </c>
     </row>
@@ -4906,31 +4914,31 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>88.06999999999999</v>
+        <v>313.59</v>
       </c>
       <c r="E125" t="n">
-        <v>80.56999999999999</v>
+        <v>239.42</v>
       </c>
       <c r="F125" t="n">
-        <v>5.95</v>
+        <v>11.61</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>[1306.07, 1156.95, 1374.1]</t>
+          <t>[1709.37, 1761.63, 1276.07]</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>[1336.93, 1269.08, 1472.82]</t>
+          <t>[1838.46, 2285.11, 1341.74]</t>
         </is>
       </c>
     </row>
@@ -4942,31 +4950,31 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>98.37</v>
+        <v>299.94</v>
       </c>
       <c r="E126" t="n">
-        <v>97.29000000000001</v>
+        <v>198.06</v>
       </c>
       <c r="F126" t="n">
-        <v>7.3</v>
+        <v>9.59</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>[1155.57, 1372.71, 1349.78]</t>
+          <t>[1769.31, 1282.91, 1055.8]</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>[1269.08, 1472.82, 1271.54]</t>
+          <t>[2285.11, 1341.74, 1075.34]</t>
         </is>
       </c>
     </row>
@@ -4978,31 +4986,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>112.54</v>
+        <v>30.51</v>
       </c>
       <c r="E127" t="n">
-        <v>109.13</v>
+        <v>25.49</v>
       </c>
       <c r="F127" t="n">
-        <v>7.51</v>
+        <v>2.1</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>[1386.28, 1364.55, 1433.54]</t>
+          <t>[1304.11, 1077.13, 1072.55]</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>[1472.82, 1271.54, 1581.37]</t>
+          <t>[1341.74, 1075.34, 1109.61]</t>
         </is>
       </c>
     </row>
@@ -5014,31 +5022,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>123.95</v>
+        <v>89.77</v>
       </c>
       <c r="E128" t="n">
-        <v>122.77</v>
+        <v>63.23</v>
       </c>
       <c r="F128" t="n">
-        <v>8.039999999999999</v>
+        <v>4.68</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>[1370.72, 1442.63, 1594.55]</t>
+          <t>[1079.07, 1075.25, 1278.29]</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>[1271.54, 1581.37, 1724.95]</t>
+          <t>[1075.34, 1109.61, 1429.88]</t>
         </is>
       </c>
     </row>
@@ -5050,31 +5058,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>144.92</v>
+        <v>184.59</v>
       </c>
       <c r="E129" t="n">
-        <v>144.89</v>
+        <v>150.59</v>
       </c>
       <c r="F129" t="n">
-        <v>8.380000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>[1432.82, 1582.99, 1775.3]</t>
+          <t>[1084.29, 1289.59, 1177.81]</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>[1581.37, 1724.95, 1919.48]</t>
+          <t>[1109.61, 1429.88, 1463.98]</t>
         </is>
       </c>
     </row>
@@ -5086,31 +5094,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>133.62</v>
+        <v>201.18</v>
       </c>
       <c r="E130" t="n">
-        <v>133.32</v>
+        <v>191.86</v>
       </c>
       <c r="F130" t="n">
-        <v>7.31</v>
+        <v>12.88</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>[1598.14, 1792.27, 1692.53]</t>
+          <t>[1304.43, 1192.19, 1399.81]</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>[1724.95, 1919.48, 1838.46]</t>
+          <t>[1429.88, 1463.98, 1578.15]</t>
         </is>
       </c>
     </row>
@@ -5122,31 +5130,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>322.45</v>
+        <v>179.99</v>
       </c>
       <c r="E131" t="n">
-        <v>260.64</v>
+        <v>169.79</v>
       </c>
       <c r="F131" t="n">
-        <v>12.21</v>
+        <v>11.32</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>[1801.22, 1703.75, 1756.16]</t>
+          <t>[1213.63, 1426.61, 1373.58]</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>[1919.48, 1838.46, 2285.11]</t>
+          <t>[1463.98, 1578.15, 1481.05]</t>
         </is>
       </c>
     </row>
@@ -5158,31 +5166,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>52.98</v>
+        <v>47</v>
       </c>
       <c r="E132" t="n">
-        <v>50.64</v>
+        <v>43.85</v>
       </c>
       <c r="F132" t="n">
-        <v>46.86</v>
+        <v>33.72</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>[126.16, 197.9, 147.25]</t>
+          <t>[140.35, 297.89, 188.02]</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>[95.22, 128.9, 95.28]</t>
+          <t>[84.38, 242.24, 168.08]</t>
         </is>
       </c>
     </row>
@@ -5194,31 +5202,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>39.57</v>
+        <v>38</v>
       </c>
       <c r="E133" t="n">
-        <v>38.82</v>
+        <v>29.14</v>
       </c>
       <c r="F133" t="n">
-        <v>28.95</v>
+        <v>13</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>[178.43, 130.38, 242.47]</t>
+          <t>[305.4, 185.14, 265.27]</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>[128.9, 95.28, 274.28]</t>
+          <t>[242.24, 168.08, 258.08]</t>
         </is>
       </c>
     </row>
@@ -5230,31 +5238,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>57.36</v>
+        <v>348.94</v>
       </c>
       <c r="E134" t="n">
-        <v>49.33</v>
+        <v>208.79</v>
       </c>
       <c r="F134" t="n">
-        <v>30.61</v>
+        <v>42.93</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>[132.82, 253.42, 110.3]</t>
+          <t>[184.36, 264.06, 1121.41]</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>[95.28, 274.28, 199.88]</t>
+          <t>[168.08, 258.08, 517.28]</t>
         </is>
       </c>
     </row>
@@ -5266,31 +5274,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>60.29</v>
+        <v>345.17</v>
       </c>
       <c r="E135" t="n">
-        <v>54.7</v>
+        <v>222.5</v>
       </c>
       <c r="F135" t="n">
-        <v>24.89</v>
+        <v>62.38</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>[230.69, 110.1, 252.72]</t>
+          <t>[261.35, 1110.94, 169.8]</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>[274.28, 199.88, 221.98]</t>
+          <t>[258.08, 517.28, 99.24]</t>
         </is>
       </c>
     </row>
@@ -5302,31 +5310,31 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>63.24</v>
+        <v>341.58</v>
       </c>
       <c r="E136" t="n">
-        <v>58.52</v>
+        <v>259.67</v>
       </c>
       <c r="F136" t="n">
-        <v>37.7</v>
+        <v>95.05</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>[110.28, 253.25, 155.68]</t>
+          <t>[1088.1, 167.76, 271.77]</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>[199.88, 221.98, 100.98]</t>
+          <t>[517.28, 99.24, 132.08]</t>
         </is>
       </c>
     </row>
@@ -5338,31 +5346,31 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>37.48</v>
+        <v>88.14</v>
       </c>
       <c r="E137" t="n">
-        <v>35.67</v>
+        <v>79.33</v>
       </c>
       <c r="F137" t="n">
-        <v>34.66</v>
+        <v>68.45</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>[241.39, 145.1, 127.86]</t>
+          <t>[165.16, 263.7, 143.5]</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>[221.98, 100.98, 84.38]</t>
+          <t>[99.24, 132.08, 103.05]</t>
         </is>
       </c>
     </row>
@@ -5374,31 +5382,31 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>61.51</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="E138" t="n">
-        <v>61.46</v>
+        <v>52.16</v>
       </c>
       <c r="F138" t="n">
-        <v>52.22</v>
+        <v>41.87</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>[161.3, 143.55, 307.14]</t>
+          <t>[253.44, 137.6, 278.92]</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>[100.98, 84.38, 242.24]</t>
+          <t>[132.08, 103.05, 279.48]</t>
         </is>
       </c>
     </row>
@@ -5410,31 +5418,31 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>47</v>
+        <v>48.16</v>
       </c>
       <c r="E139" t="n">
-        <v>43.85</v>
+        <v>37.23</v>
       </c>
       <c r="F139" t="n">
-        <v>33.72</v>
+        <v>74.08</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>[140.35, 297.89, 188.02]</t>
+          <t>[137.98, 278.47, 116.05]</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>[84.38, 242.24, 168.08]</t>
+          <t>[103.05, 279.48, 40.3]</t>
         </is>
       </c>
     </row>
@@ -5446,31 +5454,31 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>38</v>
+        <v>42.28</v>
       </c>
       <c r="E140" t="n">
-        <v>29.14</v>
+        <v>28.97</v>
       </c>
       <c r="F140" t="n">
-        <v>13</v>
+        <v>61.91</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>[305.4, 185.14, 265.27]</t>
+          <t>[274.4, 112.75, 235.38]</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>[242.24, 168.08, 258.08]</t>
+          <t>[279.48, 40.3, 226.0]</t>
         </is>
       </c>
     </row>
@@ -5482,31 +5490,31 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>348.94</v>
+        <v>42.81</v>
       </c>
       <c r="E141" t="n">
-        <v>208.79</v>
+        <v>33.27</v>
       </c>
       <c r="F141" t="n">
-        <v>42.93</v>
+        <v>66.47</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>[184.36, 264.06, 1121.41]</t>
+          <t>[108.0, 224.07, 128.84]</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>[168.08, 258.08, 517.28]</t>
+          <t>[40.3, 226.0, 98.66]</t>
         </is>
       </c>
     </row>
@@ -5518,31 +5526,31 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1550.21</v>
+        <v>1646.47</v>
       </c>
       <c r="E142" t="n">
-        <v>1470.55</v>
+        <v>1384.43</v>
       </c>
       <c r="F142" t="n">
-        <v>68.87</v>
+        <v>31.38</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>[3926.22, 3828.77, 3739.8]</t>
+          <t>[2544.48, 2828.62, 2501.56]</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>[1776.37, 2576.03, 2730.73]</t>
+          <t>[3114.29, 5453.19, 3460.45]</t>
         </is>
       </c>
     </row>
@@ -5554,31 +5562,31 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>638.04</v>
+        <v>3143.68</v>
       </c>
       <c r="E143" t="n">
-        <v>620.28</v>
+        <v>2554.62</v>
       </c>
       <c r="F143" t="n">
-        <v>25.13</v>
+        <v>49.11</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>[3255.87, 3145.59, 3031.84]</t>
+          <t>[4181.2, 4706.76, 10992.87]</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>[2576.03, 2730.73, 2265.69]</t>
+          <t>[5453.19, 3460.45, 5847.3]</t>
         </is>
       </c>
     </row>
@@ -5590,31 +5598,31 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>450</v>
+        <v>3668.29</v>
       </c>
       <c r="E144" t="n">
-        <v>415.86</v>
+        <v>2775.39</v>
       </c>
       <c r="F144" t="n">
-        <v>17.14</v>
+        <v>49.85</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>[3040.86, 2924.04, 2815.27]</t>
+          <t>[4844.31, 11997.65, 18860.21]</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>[2730.73, 2265.69, 2536.16]</t>
+          <t>[3460.45, 5847.3, 18068.25]</t>
         </is>
       </c>
     </row>
@@ -5626,31 +5634,31 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1777.77</v>
+        <v>4298.33</v>
       </c>
       <c r="E145" t="n">
-        <v>1266.11</v>
+        <v>3207.15</v>
       </c>
       <c r="F145" t="n">
-        <v>29</v>
+        <v>53.33</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[2846.61, 2736.32, 2626.84]</t>
+          <t>[13022.7, 19980.12, 1465.69]</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>[2265.69, 2536.16, 5644.09]</t>
+          <t>[5847.3, 18068.25, 1999.86]</t>
         </is>
       </c>
     </row>
@@ -5662,31 +5670,31 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1924.1</v>
+        <v>3142.62</v>
       </c>
       <c r="E146" t="n">
-        <v>1453.16</v>
+        <v>2517.18</v>
       </c>
       <c r="F146" t="n">
-        <v>30.37</v>
+        <v>42.8</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>[2625.65, 2513.61, 2409.73]</t>
+          <t>[12894.87, 945.85, 1489.06]</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>[2536.16, 5644.09, 3549.25]</t>
+          <t>[18068.25, 1999.86, 2813.21]</t>
         </is>
       </c>
     </row>
@@ -5698,31 +5706,31 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1990.1</v>
+        <v>1186.75</v>
       </c>
       <c r="E147" t="n">
-        <v>1705.39</v>
+        <v>1174.4</v>
       </c>
       <c r="F147" t="n">
-        <v>38.17</v>
+        <v>44.66</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>[2500.8, 2396.8, 2293.86]</t>
+          <t>[1062.94, 1481.9, 1897.42]</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>[5644.09, 3549.25, 3114.29]</t>
+          <t>[1999.86, 2813.21, 3152.38]</t>
         </is>
       </c>
     </row>
@@ -5734,31 +5742,31 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2186.74</v>
+        <v>484.86</v>
       </c>
       <c r="E148" t="n">
-        <v>1762.4</v>
+        <v>438.94</v>
       </c>
       <c r="F148" t="n">
-        <v>39.57</v>
+        <v>15.42</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>[3011.68, 1917.85, 1900.01]</t>
+          <t>[2084.07, 2836.77, 2362.33]</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>[3549.25, 3114.29, 5453.19]</t>
+          <t>[2813.21, 3152.38, 2634.39]</t>
         </is>
       </c>
     </row>
@@ -5770,31 +5778,31 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1646.47</v>
+        <v>184.79</v>
       </c>
       <c r="E149" t="n">
-        <v>1384.43</v>
+        <v>156.55</v>
       </c>
       <c r="F149" t="n">
-        <v>31.38</v>
+        <v>5.41</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>[2544.48, 2828.62, 2501.56]</t>
+          <t>[2903.97, 2433.6, 2736.88]</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>[3114.29, 5453.19, 3460.45]</t>
+          <t>[3152.38, 2634.39, 2757.33]</t>
         </is>
       </c>
     </row>
@@ -5806,31 +5814,31 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3143.68</v>
+        <v>272.78</v>
       </c>
       <c r="E150" t="n">
-        <v>2554.62</v>
+        <v>216.12</v>
       </c>
       <c r="F150" t="n">
-        <v>49.11</v>
+        <v>4.8</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>[4181.2, 4706.76, 10992.87]</t>
+          <t>[2625.01, 2979.41, 6549.0]</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>[5453.19, 3460.45, 5847.3]</t>
+          <t>[2634.39, 2757.33, 6965.91]</t>
         </is>
       </c>
     </row>
@@ -5842,31 +5850,31 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>3668.29</v>
+        <v>1144.59</v>
       </c>
       <c r="E151" t="n">
-        <v>2775.39</v>
+        <v>848.86</v>
       </c>
       <c r="F151" t="n">
-        <v>49.85</v>
+        <v>32.78</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>[4844.31, 11997.65, 18860.21]</t>
+          <t>[2998.41, 6592.43, 4225.92]</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[3460.45, 5847.3, 18068.25]</t>
+          <t>[2757.33, 6965.91, 2293.91]</t>
         </is>
       </c>
     </row>
@@ -5878,31 +5886,31 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>2725.74</v>
+        <v>2366.91</v>
       </c>
       <c r="E152" t="n">
-        <v>2708.5</v>
+        <v>1919.69</v>
       </c>
       <c r="F152" t="n">
-        <v>108.64</v>
+        <v>28.2</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>[4760.89, 4774.73, 4787.71]</t>
+          <t>[2598.25, 9643.55, 9935.14]</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>[2364.3, 1650.36, 7392.25]</t>
+          <t>[2568.13, 7223.75, 6626.0]</t>
         </is>
       </c>
     </row>
@@ -5914,31 +5922,31 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2662.02</v>
+        <v>5009.96</v>
       </c>
       <c r="E153" t="n">
-        <v>2615.17</v>
+        <v>4459.9</v>
       </c>
       <c r="F153" t="n">
-        <v>99.55</v>
+        <v>66.05</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>[4144.55, 4116.72, 4087.17]</t>
+          <t>[9643.26, 9940.2, 14315.31]</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>[1650.36, 7392.25, 2011.37]</t>
+          <t>[7223.75, 6626.0, 6669.33]</t>
         </is>
       </c>
     </row>
@@ -5950,31 +5958,31 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2431.54</v>
+        <v>5360.89</v>
       </c>
       <c r="E154" t="n">
-        <v>1968.13</v>
+        <v>5117.62</v>
       </c>
       <c r="F154" t="n">
-        <v>47.78</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>[3456.74, 3389.92, 3326.48]</t>
+          <t>[9828.21, 13780.0, 17453.15]</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>[7392.25, 2011.37, 2736.15]</t>
+          <t>[6626.0, 6669.33, 12413.16]</t>
         </is>
       </c>
     </row>
@@ -5986,31 +5994,31 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>3175.5</v>
+        <v>5883.04</v>
       </c>
       <c r="E155" t="n">
-        <v>2682.46</v>
+        <v>4761.29</v>
       </c>
       <c r="F155" t="n">
-        <v>63.82</v>
+        <v>58.7</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>[3894.4, 3855.42, 3815.54]</t>
+          <t>[15022.03, 18248.72, 2584.72]</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>[2011.37, 2736.15, 8860.62]</t>
+          <t>[6669.33, 12413.16, 2489.12]</t>
         </is>
       </c>
     </row>
@@ -6022,31 +6030,31 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3285.58</v>
+        <v>512.28</v>
       </c>
       <c r="E156" t="n">
-        <v>2533.27</v>
+        <v>489.59</v>
       </c>
       <c r="F156" t="n">
-        <v>53.86</v>
+        <v>15.26</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>[3455.32, 3395.92, 3339.42]</t>
+          <t>[12967.64, 1856.07, 1489.12]</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>[2736.15, 8860.62, 1923.47]</t>
+          <t>[12413.16, 2489.12, 1770.35]</t>
         </is>
       </c>
     </row>
@@ -6058,31 +6066,31 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>3335.12</v>
+        <v>1449.95</v>
       </c>
       <c r="E157" t="n">
-        <v>2477.73</v>
+        <v>1115.92</v>
       </c>
       <c r="F157" t="n">
-        <v>50.29</v>
+        <v>24.57</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>[3252.29, 3189.86, 3126.6]</t>
+          <t>[1837.73, 1482.26, 5291.57]</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>[8860.62, 1923.47, 2568.13]</t>
+          <t>[2489.12, 1770.35, 7699.85]</t>
         </is>
       </c>
     </row>
@@ -6094,31 +6102,31 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1337.22</v>
+        <v>1076.59</v>
       </c>
       <c r="E158" t="n">
-        <v>1314.25</v>
+        <v>915.96</v>
       </c>
       <c r="F158" t="n">
-        <v>42.83</v>
+        <v>24.19</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>[679.07, 1515.08, 5578.45]</t>
+          <t>[1444.29, 6020.85, 1553.6]</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>[1923.47, 2568.13, 7223.75]</t>
+          <t>[1770.35, 7699.85, 2296.43]</t>
         </is>
       </c>
     </row>
@@ -6130,31 +6138,31 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2366.91</v>
+        <v>602.28</v>
       </c>
       <c r="E159" t="n">
-        <v>1919.69</v>
+        <v>556.8099999999999</v>
       </c>
       <c r="F159" t="n">
-        <v>28.2</v>
+        <v>14.65</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>[2598.25, 9643.55, 9935.14]</t>
+          <t>[6830.9, 1818.25, 2409.95]</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>[2568.13, 7223.75, 6626.0]</t>
+          <t>[7699.85, 2296.43, 2733.24]</t>
         </is>
       </c>
     </row>
@@ -6166,31 +6174,31 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5009.96</v>
+        <v>445.5</v>
       </c>
       <c r="E160" t="n">
-        <v>4459.9</v>
+        <v>406.08</v>
       </c>
       <c r="F160" t="n">
-        <v>66.05</v>
+        <v>10.08</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[9643.26, 9940.2, 14315.31]</t>
+          <t>[1928.12, 2530.27, 8880.97]</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>[7223.75, 6626.0, 6669.33]</t>
+          <t>[2296.43, 2733.24, 9527.94]</t>
         </is>
       </c>
     </row>
@@ -6202,31 +6210,31 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>5360.89</v>
+        <v>237.69</v>
       </c>
       <c r="E161" t="n">
-        <v>5117.62</v>
+        <v>185.13</v>
       </c>
       <c r="F161" t="n">
-        <v>65.18000000000001</v>
+        <v>4.83</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>[9828.21, 13780.0, 17453.15]</t>
+          <t>[2779.89, 9919.97, 1461.12]</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>[6626.0, 6669.33, 12413.16]</t>
+          <t>[2733.24, 9527.94, 1344.41]</t>
         </is>
       </c>
     </row>
@@ -6238,31 +6246,31 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>543.91</v>
+        <v>330.61</v>
       </c>
       <c r="E162" t="n">
-        <v>374.6</v>
+        <v>274.29</v>
       </c>
       <c r="F162" t="n">
-        <v>38.79</v>
+        <v>49.18</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>[366.39, 342.04, 320.72]</t>
+          <t>[130.3, 774.65, 170.62]</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>[1298.35, 454.7, 399.9]</t>
+          <t>[593.1, 750.95, 507.0]</t>
         </is>
       </c>
     </row>
@@ -6274,31 +6282,31 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>129.12</v>
+        <v>688.48</v>
       </c>
       <c r="E163" t="n">
-        <v>85.58</v>
+        <v>518.28</v>
       </c>
       <c r="F163" t="n">
-        <v>44.04</v>
+        <v>178.78</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>[442.44, 422.2, 401.58]</t>
+          <t>[844.75, 192.33, 1394.63]</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>[454.7, 399.9, 179.4]</t>
+          <t>[750.95, 507.0, 248.25]</t>
         </is>
       </c>
     </row>
@@ -6310,31 +6318,31 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>134.39</v>
+        <v>2121.71</v>
       </c>
       <c r="E164" t="n">
-        <v>101.33</v>
+        <v>1651.59</v>
       </c>
       <c r="F164" t="n">
-        <v>48</v>
+        <v>279.01</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>[425.06, 404.48, 385.52]</t>
+          <t>[191.01, 1417.43, 4611.89]</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>[399.9, 179.4, 439.25]</t>
+          <t>[507.0, 248.25, 1142.3]</t>
         </is>
       </c>
     </row>
@@ -6346,31 +6354,31 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>310.59</v>
+        <v>1787.28</v>
       </c>
       <c r="E165" t="n">
-        <v>255.62</v>
+        <v>1531.24</v>
       </c>
       <c r="F165" t="n">
-        <v>64.34</v>
+        <v>224.94</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>[397.6, 378.54, 359.8]</t>
+          <t>[1145.24, 3976.96, 457.07]</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>[179.4, 439.25, 847.75]</t>
+          <t>[248.25, 1142.3, 1319.15]</t>
         </is>
       </c>
     </row>
@@ -6382,31 +6390,31 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>335.83</v>
+        <v>2250.21</v>
       </c>
       <c r="E166" t="n">
-        <v>280.24</v>
+        <v>1601.37</v>
       </c>
       <c r="F166" t="n">
-        <v>94.25</v>
+        <v>143.51</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>[329.36, 310.27, 292.85]</t>
+          <t>[4943.36, 471.81, 308.36]</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>[439.25, 847.75, 99.5]</t>
+          <t>[1142.3, 1319.15, 464.08]</t>
         </is>
       </c>
     </row>
@@ -6418,31 +6426,31 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>369.29</v>
+        <v>317.65</v>
       </c>
       <c r="E167" t="n">
-        <v>344.73</v>
+        <v>242.23</v>
       </c>
       <c r="F167" t="n">
-        <v>107.07</v>
+        <v>28.23</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>[324.15, 306.76, 289.76]</t>
+          <t>[793.48, 308.02, 356.09]</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>[847.75, 99.5, 593.1]</t>
+          <t>[1319.15, 464.08, 401.05]</t>
         </is>
       </c>
     </row>
@@ -6454,31 +6462,31 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>276.35</v>
+        <v>121.83</v>
       </c>
       <c r="E168" t="n">
-        <v>181.04</v>
+        <v>86.59</v>
       </c>
       <c r="F168" t="n">
-        <v>38.43</v>
+        <v>21.19</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>[69.57, 116.8, 714.06]</t>
+          <t>[256.57, 367.68, 160.69]</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>[99.5, 593.1, 750.95]</t>
+          <t>[464.08, 401.05, 179.6]</t>
         </is>
       </c>
     </row>
@@ -6490,31 +6498,31 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>330.61</v>
+        <v>36.69</v>
       </c>
       <c r="E169" t="n">
-        <v>274.29</v>
+        <v>28.2</v>
       </c>
       <c r="F169" t="n">
-        <v>49.18</v>
+        <v>7.4</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>[130.3, 774.65, 170.62]</t>
+          <t>[385.94, 171.26, 382.3]</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>[593.1, 750.95, 507.0]</t>
+          <t>[401.05, 179.6, 443.45]</t>
         </is>
       </c>
     </row>
@@ -6526,31 +6534,31 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>688.48</v>
+        <v>57.7</v>
       </c>
       <c r="E170" t="n">
-        <v>518.28</v>
+        <v>48.98</v>
       </c>
       <c r="F170" t="n">
-        <v>178.78</v>
+        <v>8.98</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>[844.75, 192.33, 1394.63]</t>
+          <t>[172.06, 384.12, 774.64]</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>[750.95, 507.0, 248.25]</t>
+          <t>[179.6, 443.45, 854.7]</t>
         </is>
       </c>
     </row>
@@ -6562,31 +6570,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2121.71</v>
+        <v>60.58</v>
       </c>
       <c r="E171" t="n">
-        <v>1651.59</v>
+        <v>52.38</v>
       </c>
       <c r="F171" t="n">
-        <v>279.01</v>
+        <v>11.94</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>[191.01, 1417.43, 4611.89]</t>
+          <t>[387.02, 767.24, 89.85]</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>[507.0, 248.25, 1142.3]</t>
+          <t>[443.45, 854.7, 103.1]</t>
         </is>
       </c>
     </row>
@@ -6598,31 +6606,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>417.07</v>
+        <v>723.9</v>
       </c>
       <c r="E172" t="n">
-        <v>305.62</v>
+        <v>570.99</v>
       </c>
       <c r="F172" t="n">
-        <v>11.15</v>
+        <v>13.96</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>[2496.63, 2982.98, 3439.45]</t>
+          <t>[2884.04, 3600.54, 4575.11]</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>[2459.35, 2801.67, 2741.18]</t>
+          <t>[4061.35, 4014.27, 4697.04]</t>
         </is>
       </c>
     </row>
@@ -6634,31 +6642,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>428.23</v>
+        <v>295.53</v>
       </c>
       <c r="E173" t="n">
-        <v>347.54</v>
+        <v>249.46</v>
       </c>
       <c r="F173" t="n">
-        <v>12.5</v>
+        <v>5.17</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>[2997.51, 3441.4, 2801.48]</t>
+          <t>[3667.35, 4671.08, 6321.79]</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>[2801.67, 2741.18, 2948.03]</t>
+          <t>[4014.27, 4697.04, 5946.29]</t>
         </is>
       </c>
     </row>
@@ -6670,31 +6678,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>413.35</v>
+        <v>269.95</v>
       </c>
       <c r="E174" t="n">
-        <v>349.42</v>
+        <v>195.75</v>
       </c>
       <c r="F174" t="n">
-        <v>12.27</v>
+        <v>3.19</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>[3402.35, 2770.3, 2931.09]</t>
+          <t>[4718.63, 6399.66, 7426.21]</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>[2741.18, 2948.03, 3140.46]</t>
+          <t>[4697.04, 5946.29, 7538.52]</t>
         </is>
       </c>
     </row>
@@ -6706,31 +6714,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>619.5599999999999</v>
+        <v>348.84</v>
       </c>
       <c r="E175" t="n">
-        <v>501.25</v>
+        <v>311.08</v>
       </c>
       <c r="F175" t="n">
-        <v>12.68</v>
+        <v>7.72</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>[2727.22, 2873.04, 3593.86]</t>
+          <t>[6438.48, 7431.03, 2812.46]</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>[2948.03, 3140.46, 4609.38]</t>
+          <t>[5946.29, 7538.52, 2478.9]</t>
         </is>
       </c>
     </row>
@@ -6742,31 +6750,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1129.99</v>
+        <v>547.98</v>
       </c>
       <c r="E176" t="n">
-        <v>966.78</v>
+        <v>442.54</v>
       </c>
       <c r="F176" t="n">
-        <v>20.2</v>
+        <v>16.94</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>[2897.33, 3627.99, 3630.77]</t>
+          <t>[7416.63, 2799.74, 3324.38]</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>[3140.46, 4609.38, 5306.59]</t>
+          <t>[7538.52, 2478.9, 2439.47]</t>
         </is>
       </c>
     </row>
@@ -6778,31 +6786,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1335.86</v>
+        <v>746.71</v>
       </c>
       <c r="E177" t="n">
-        <v>1305.64</v>
+        <v>706.49</v>
       </c>
       <c r="F177" t="n">
-        <v>28.04</v>
+        <v>27.35</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>[3654.5, 3659.77, 2746.14]</t>
+          <t>[2869.15, 3416.64, 3616.25]</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>[4609.38, 5306.59, 4061.35]</t>
+          <t>[2478.9, 2439.47, 2864.2]</t>
         </is>
       </c>
     </row>
@@ -6814,31 +6822,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1210.38</v>
+        <v>643.9</v>
       </c>
       <c r="E178" t="n">
-        <v>1126.51</v>
+        <v>550.22</v>
       </c>
       <c r="F178" t="n">
-        <v>24.73</v>
+        <v>21.03</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>[3719.34, 2798.07, 3485.28]</t>
+          <t>[3339.23, 3515.62, 2972.14]</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>[5306.59, 4061.35, 4014.27]</t>
+          <t>[2439.47, 2864.2, 2872.67]</t>
         </is>
       </c>
     </row>
@@ -6850,31 +6858,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>723.9</v>
+        <v>404.31</v>
       </c>
       <c r="E179" t="n">
-        <v>570.99</v>
+        <v>331.84</v>
       </c>
       <c r="F179" t="n">
-        <v>13.96</v>
+        <v>11.86</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>[2884.04, 3600.54, 4575.11]</t>
+          <t>[3430.9, 2890.46, 3117.79]</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>[4061.35, 4014.27, 4697.04]</t>
+          <t>[2864.2, 2872.67, 2706.78]</t>
         </is>
       </c>
     </row>
@@ -6886,31 +6894,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>295.53</v>
+        <v>305.83</v>
       </c>
       <c r="E180" t="n">
-        <v>249.46</v>
+        <v>265.4</v>
       </c>
       <c r="F180" t="n">
-        <v>5.17</v>
+        <v>7.96</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>[3667.35, 4671.08, 6321.79]</t>
+          <t>[2817.29, 3037.77, 3810.41]</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>[4014.27, 4697.04, 5946.29]</t>
+          <t>[2872.67, 2706.78, 4220.25]</t>
         </is>
       </c>
     </row>
@@ -6922,31 +6930,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>269.95</v>
+        <v>560.41</v>
       </c>
       <c r="E181" t="n">
-        <v>195.75</v>
+        <v>517.4299999999999</v>
       </c>
       <c r="F181" t="n">
-        <v>3.19</v>
+        <v>13.07</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>[4718.63, 6399.66, 7426.21]</t>
+          <t>[3061.4, 3844.15, 3959.2]</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>[4697.04, 5946.29, 7538.52]</t>
+          <t>[2706.78, 4220.25, 4780.77]</t>
         </is>
       </c>
     </row>
@@ -6958,31 +6966,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>586.28</v>
+        <v>337.22</v>
       </c>
       <c r="E182" t="n">
-        <v>427.6</v>
+        <v>278.51</v>
       </c>
       <c r="F182" t="n">
-        <v>13.39</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>[4934.37, 2524.57, 1515.91]</t>
+          <t>[3460.26, 5532.18, 1986.16]</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>[3942.12, 2622.99, 1708.04]</t>
+          <t>[3472.15, 5090.14, 2367.75]</t>
         </is>
       </c>
     </row>
@@ -6994,31 +7002,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>211.84</v>
+        <v>354.28</v>
       </c>
       <c r="E183" t="n">
-        <v>191.84</v>
+        <v>335.38</v>
       </c>
       <c r="F183" t="n">
-        <v>9.710000000000001</v>
+        <v>11.21</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>[2400.92, 1424.43, 1644.48]</t>
+          <t>[5535.52, 1985.0, 1863.63]</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>[2622.99, 1708.04, 1714.33]</t>
+          <t>[5090.14, 2367.75, 2041.65]</t>
         </is>
       </c>
     </row>
@@ -7030,31 +7038,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>190.2</v>
+        <v>449.92</v>
       </c>
       <c r="E184" t="n">
-        <v>164.77</v>
+        <v>410.24</v>
       </c>
       <c r="F184" t="n">
-        <v>9.210000000000001</v>
+        <v>14.39</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>[1459.06, 1682.34, 1694.39]</t>
+          <t>[1971.36, 1850.46, 3129.03]</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>[1708.04, 1714.33, 1907.73]</t>
+          <t>[2367.75, 2041.65, 3772.16]</t>
         </is>
       </c>
     </row>
@@ -7066,31 +7074,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>314.09</v>
+        <v>361.13</v>
       </c>
       <c r="E185" t="n">
-        <v>243.78</v>
+        <v>269.41</v>
       </c>
       <c r="F185" t="n">
-        <v>15.63</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>[1689.05, 1706.43, 943.19]</t>
+          <t>[1872.99, 3171.06, 4046.24]</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>[1714.33, 1907.73, 1447.97]</t>
+          <t>[2041.65, 3772.16, 4007.77]</t>
         </is>
       </c>
     </row>
@@ -7102,31 +7110,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>317.94</v>
+        <v>386.14</v>
       </c>
       <c r="E186" t="n">
-        <v>258.26</v>
+        <v>322.46</v>
       </c>
       <c r="F186" t="n">
-        <v>16.15</v>
+        <v>10.23</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>[1702.58, 940.74, 2283.32]</t>
+          <t>[3186.52, 4073.19, 2018.86]</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>[1907.73, 1447.97, 2345.72]</t>
+          <t>[3772.16, 4007.77, 2335.19]</t>
         </is>
       </c>
     </row>
@@ -7138,31 +7146,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>309.61</v>
+        <v>461.17</v>
       </c>
       <c r="E187" t="n">
-        <v>244.33</v>
+        <v>379.96</v>
       </c>
       <c r="F187" t="n">
-        <v>14.04</v>
+        <v>16.96</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>[944.18, 2292.4, 3296.27]</t>
+          <t>[4124.2, 2047.89, 1328.11]</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>[1447.97, 2345.72, 3472.15]</t>
+          <t>[4007.77, 2335.19, 2064.27]</t>
         </is>
       </c>
     </row>
@@ -7174,31 +7182,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>264.55</v>
+        <v>461.94</v>
       </c>
       <c r="E188" t="n">
-        <v>171.26</v>
+        <v>379.71</v>
       </c>
       <c r="F188" t="n">
-        <v>3.78</v>
+        <v>18.35</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>[2397.5, 3465.38, 5545.36]</t>
+          <t>[2047.79, 1326.28, 1512.23]</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>[2345.72, 3472.15, 5090.14]</t>
+          <t>[2335.19, 2064.27, 1625.97]</t>
         </is>
       </c>
     </row>
@@ -7210,31 +7218,31 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>337.22</v>
+        <v>444.21</v>
       </c>
       <c r="E189" t="n">
-        <v>278.51</v>
+        <v>355.03</v>
       </c>
       <c r="F189" t="n">
-        <v>8.380000000000001</v>
+        <v>18.07</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>[3460.26, 5532.18, 1986.16]</t>
+          <t>[1342.82, 1532.98, 1598.74]</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>[3472.15, 5090.14, 2367.75]</t>
+          <t>[2064.27, 1625.97, 1849.39]</t>
         </is>
       </c>
     </row>
@@ -7246,31 +7254,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>354.28</v>
+        <v>295.13</v>
       </c>
       <c r="E190" t="n">
-        <v>335.38</v>
+        <v>232.34</v>
       </c>
       <c r="F190" t="n">
-        <v>11.21</v>
+        <v>15.26</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>[5535.52, 1985.0, 1863.63]</t>
+          <t>[1590.72, 1661.84, 941.95]</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>[5090.14, 2367.75, 2041.65]</t>
+          <t>[1625.97, 1849.39, 1416.17]</t>
         </is>
       </c>
     </row>
@@ -7282,31 +7290,31 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>449.92</v>
+        <v>298.45</v>
       </c>
       <c r="E191" t="n">
-        <v>410.24</v>
+        <v>256.82</v>
       </c>
       <c r="F191" t="n">
-        <v>14.39</v>
+        <v>16.02</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>[1971.36, 1850.46, 3129.03]</t>
+          <t>[1672.18, 946.57, 2200.51]</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>[2367.75, 2041.65, 3772.16]</t>
+          <t>[1849.39, 1416.17, 2324.16]</t>
         </is>
       </c>
     </row>
@@ -7318,31 +7326,31 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2764.34</v>
+        <v>3984.88</v>
       </c>
       <c r="E192" t="n">
-        <v>1781.88</v>
+        <v>2861.59</v>
       </c>
       <c r="F192" t="n">
-        <v>17.24</v>
+        <v>20.49</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>[6509.55, 6254.1, 7472.22]</t>
+          <t>[8283.51, 8960.47, 11284.4]</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>[6351.97, 11020.91, 7050.97]</t>
+          <t>[9372.79, 15738.07, 10566.5]</t>
         </is>
       </c>
     </row>
@@ -7354,31 +7362,31 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>3341.64</v>
+        <v>3811.6</v>
       </c>
       <c r="E193" t="n">
-        <v>2764.67</v>
+        <v>2777.76</v>
       </c>
       <c r="F193" t="n">
-        <v>27.45</v>
+        <v>19.41</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>[6165.18, 7353.99, 6088.76]</t>
+          <t>[9274.82, 11678.71, 12199.79]</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>[11020.91, 7050.97, 9224.01]</t>
+          <t>[15738.07, 10566.5, 11441.98]</t>
         </is>
       </c>
     </row>
@@ -7390,31 +7398,31 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1538.99</v>
+        <v>7812.69</v>
       </c>
       <c r="E194" t="n">
-        <v>1330.03</v>
+        <v>5549.98</v>
       </c>
       <c r="F194" t="n">
-        <v>16.42</v>
+        <v>25.24</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>[8417.78, 6964.62, 7140.05]</t>
+          <t>[12320.25, 13012.57, 16027.63]</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>[7050.97, 9224.01, 6776.16]</t>
+          <t>[10566.5, 11441.98, 29353.24]</t>
         </is>
       </c>
     </row>
@@ -7426,31 +7434,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>4942.44</v>
+        <v>7853.55</v>
       </c>
       <c r="E195" t="n">
-        <v>3610.1</v>
+        <v>5033.24</v>
       </c>
       <c r="F195" t="n">
-        <v>27.21</v>
+        <v>20.08</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>[6909.39, 7054.85, 7478.56]</t>
+          <t>[12886.49, 15828.02, 8597.16]</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>[9224.01, 6776.16, 15715.54]</t>
+          <t>[11441.98, 29353.24, 8467.16]</t>
         </is>
       </c>
     </row>
@@ -7462,31 +7470,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>4644.27</v>
+        <v>7809.18</v>
       </c>
       <c r="E196" t="n">
-        <v>2933.67</v>
+        <v>4592.23</v>
       </c>
       <c r="F196" t="n">
-        <v>20.8</v>
+        <v>16.39</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>[7208.87, 7690.41, 6605.67]</t>
+          <t>[15828.62, 8556.25, 8195.33]</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>[6776.16, 15715.54, 6948.86]</t>
+          <t>[29353.24, 8467.16, 8032.34]</t>
         </is>
       </c>
     </row>
@@ -7498,31 +7506,31 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>4772.16</v>
+        <v>1292.37</v>
       </c>
       <c r="E197" t="n">
-        <v>3387.62</v>
+        <v>1172.37</v>
       </c>
       <c r="F197" t="n">
-        <v>25.04</v>
+        <v>14.26</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>[7631.6, 6545.58, 7697.15]</t>
+          <t>[9160.92, 8922.62, 10158.1]</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>[15715.54, 6948.86, 9372.79]</t>
+          <t>[8467.16, 8032.34, 8225.02]</t>
         </is>
       </c>
     </row>
@@ -7534,31 +7542,31 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>4068.24</v>
+        <v>2397.91</v>
       </c>
       <c r="E198" t="n">
-        <v>2754.7</v>
+        <v>2132.63</v>
       </c>
       <c r="F198" t="n">
-        <v>19.53</v>
+        <v>29.5</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>[6851.98, 8143.19, 8800.45]</t>
+          <t>[8937.81, 10150.69, 10195.06]</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>[6948.86, 9372.79, 15738.07]</t>
+          <t>[8032.34, 8225.02, 6628.3]</t>
         </is>
       </c>
     </row>
@@ -7570,31 +7578,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>3984.88</v>
+        <v>2440.76</v>
       </c>
       <c r="E199" t="n">
-        <v>2861.59</v>
+        <v>2311.2</v>
       </c>
       <c r="F199" t="n">
-        <v>20.49</v>
+        <v>31.92</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>[8283.51, 8960.47, 11284.4]</t>
+          <t>[10017.97, 10048.36, 9418.15]</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>[9372.79, 15738.07, 10566.5]</t>
+          <t>[8225.02, 6628.3, 7697.58]</t>
         </is>
       </c>
     </row>
@@ -7606,31 +7614,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>3811.6</v>
+        <v>2237.45</v>
       </c>
       <c r="E200" t="n">
-        <v>2777.76</v>
+        <v>2127.17</v>
       </c>
       <c r="F200" t="n">
-        <v>19.41</v>
+        <v>28.21</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>[9274.82, 11678.71, 12199.79]</t>
+          <t>[9594.08, 8964.37, 11316.3]</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>[15738.07, 10566.5, 11441.98]</t>
+          <t>[6628.3, 7697.58, 9167.36]</t>
         </is>
       </c>
     </row>
@@ -7642,31 +7650,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>7812.69</v>
+        <v>993.98</v>
       </c>
       <c r="E201" t="n">
-        <v>5549.98</v>
+        <v>892.8</v>
       </c>
       <c r="F201" t="n">
-        <v>25.24</v>
+        <v>10.38</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>[12320.25, 13012.57, 16027.63]</t>
+          <t>[8467.39, 10646.06, 8150.39]</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>[10566.5, 11441.98, 29353.24]</t>
+          <t>[7697.58, 9167.36, 8580.29]</t>
         </is>
       </c>
     </row>
